--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -9912,158 +9912,150 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>220529</v>
+        <v>74581</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Gilson Daniel</t>
+          <t>Gilmar Machado</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>GILSON DANIEL BATISTA</t>
+          <t>GILMAR ALVES MACHADO</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsondaniel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>@gilsondaniel1919</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gilsondaniel1919</t>
-        </is>
-      </c>
+          <t>dep.gilmarmachado@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
       <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74581</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>204365</v>
+        <v>220529</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Gilson Marques</t>
+          <t>Gilson Daniel</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>GILSON MARQUES VIEIRA</t>
+          <t>GILSON DANIEL BATISTA</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsonmarques@camara.leg.br</t>
+          <t>dep.gilsondaniel@camara.leg.br</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>@gilson.marques.novo</t>
+          <t>@gilsondaniel1919</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilson.marques.novo</t>
-        </is>
-      </c>
-      <c r="I217" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/gilsonmarquesnovo</t>
-        </is>
-      </c>
+          <t>https://instagram.com/gilsondaniel1919</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>220526</v>
+        <v>204365</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Gilvan da Federal</t>
+          <t>Gilson Marques</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>GILVAN AGUIAR COSTA</t>
+          <t>GILSON MARQUES VIEIRA</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>dep.gilvandafederal@camara.leg.br</t>
+          <t>dep.gilsonmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>@gilvandafederal</t>
+          <t>@gilson.marques.novo</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilvandafederal</t>
-        </is>
-      </c>
-      <c r="I218" s="2" t="inlineStr"/>
+          <t>https://instagram.com/gilson.marques.novo</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/gilsonmarquesnovo</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>160673</v>
+        <v>220526</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Giovani Cherini</t>
+          <t>Gilvan da Federal</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>GIOVANI CHERINI</t>
+          <t>GILVAN AGUIAR COSTA</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -10073,50 +10065,58 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>dep.giovanicherini@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr"/>
+          <t>dep.gilvandafederal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>@gilvandafederal</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gilvandafederal</t>
+        </is>
+      </c>
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>152605</v>
+        <v>160673</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Glauber Braga</t>
+          <t>Giovani Cherini</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GLAUBER DE MEDEIROS BRAGA</t>
+          <t>GIOVANI CHERINI</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>dep.glauberbraga@camara.leg.br</t>
+          <t>dep.giovanicherini@camara.leg.br</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
@@ -10124,37 +10124,37 @@
       <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/152605</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>204419</v>
+        <v>152605</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Glaustin da Fokus</t>
+          <t>Glauber Braga</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GLAUSKSTON BATISTA RIOS</t>
+          <t>GLAUBER DE MEDEIROS BRAGA</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>dep.glaustindafokus@camara.leg.br</t>
+          <t>dep.glauberbraga@camara.leg.br</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr"/>
@@ -10162,37 +10162,37 @@
       <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/152605</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>236284</v>
+        <v>204419</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Glaycon Franco</t>
+          <t>Glaustin da Fokus</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>GLYCON MOREIRA FRANCO</t>
+          <t>GLAUSKSTON BATISTA RIOS</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>dep.glayconfranco@camara.leg.br</t>
+          <t>dep.glaustindafokus@camara.leg.br</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
       <c r="I222" s="2" t="inlineStr"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236284</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -16642,116 +16642,104 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>204453</v>
+        <v>220584</v>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Natália Bonavides</t>
+          <t>Murilo Galdino</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>NATÁLIA BASTOS BONAVIDES</t>
+          <t>CÁSSIO MURILO GALDINO DE ARAÚJO</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>dep.nataliabonavides@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>@nataliabonavides</t>
-        </is>
-      </c>
-      <c r="H369" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/nataliabonavides</t>
-        </is>
-      </c>
-      <c r="I369" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
-        </is>
-      </c>
+          <t>dep.murilogaldino@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr"/>
+      <c r="H369" s="2" t="inlineStr"/>
+      <c r="I369" s="2" t="inlineStr"/>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220584</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>204449</v>
+        <v>204453</v>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Nelson Barbudo</t>
+          <t>Natália Bonavides</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>NELSON NED PREVIDENTE</t>
+          <t>NATÁLIA BASTOS BONAVIDES</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>dep.nelsonbarbudo@camara.leg.br</t>
+          <t>dep.nataliabonavides@camara.leg.br</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>@nelsonbarbudo</t>
+          <t>@nataliabonavides</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsonbarbudo</t>
+          <t>https://instagram.com/nataliabonavides</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
+          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>220622</v>
+        <v>204449</v>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Nely Aquino</t>
+          <t>Nelson Barbudo</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>NELI PEREIRA DE AQUINO</t>
+          <t>NELSON NED PREVIDENTE</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -16761,181 +16749,181 @@
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>dep.nelyaquino@camara.leg.br</t>
+          <t>dep.nelsonbarbudo@camara.leg.br</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>@nelyaquinooficial</t>
+          <t>@nelsonbarbudo</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelyaquinooficial</t>
+          <t>https://instagram.com/nelsonbarbudo</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/NelyAquino</t>
+          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>220703</v>
+        <v>220622</v>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Neto Carletto</t>
+          <t>Nely Aquino</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
+          <t>NELI PEREIRA DE AQUINO</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>dep.netocarletto@camara.leg.br</t>
+          <t>dep.nelyaquino@camara.leg.br</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>@netocarletto</t>
+          <t>@nelyaquinooficial</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/netocarletto</t>
-        </is>
-      </c>
-      <c r="I372" s="2" t="inlineStr"/>
+          <t>https://instagram.com/nelyaquinooficial</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/NelyAquino</t>
+        </is>
+      </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>178896</v>
+        <v>220703</v>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Newton Cardoso Jr</t>
+          <t>Neto Carletto</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>NEWTON CARDOSO JUNIOR</t>
+          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>dep.newtoncardosojr@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G373" s="2" t="inlineStr"/>
-      <c r="H373" s="2" t="inlineStr"/>
+          <t>dep.netocarletto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>@netocarletto</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/netocarletto</t>
+        </is>
+      </c>
       <c r="I373" s="2" t="inlineStr"/>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>204479</v>
+        <v>178896</v>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Nicoletti</t>
+          <t>Newton Cardoso Jr</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS NICOLETTI</t>
+          <t>NEWTON CARDOSO JUNIOR</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>dep.nicoletti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G374" s="2" t="inlineStr">
-        <is>
-          <t>@deputadonicoletti</t>
-        </is>
-      </c>
-      <c r="H374" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadonicoletti</t>
-        </is>
-      </c>
-      <c r="I374" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/DeputadoNicoletti</t>
-        </is>
-      </c>
+          <t>dep.newtoncardosojr@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr"/>
+      <c r="H374" s="2" t="inlineStr"/>
+      <c r="I374" s="2" t="inlineStr"/>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>209787</v>
+        <v>204479</v>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Nikolas Ferreira</t>
+          <t>Nicoletti</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
+          <t>ANTONIO CARLOS NICOLETTI</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -16945,656 +16933,668 @@
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>dep.nikolasferreira@camara.leg.br</t>
+          <t>dep.nicoletti@camara.leg.br</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>@nikolasferreiradm</t>
+          <t>@deputadonicoletti</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nikolasferreiradm</t>
+          <t>https://instagram.com/deputadonicoletti</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NikolasFerreiraO</t>
+          <t>https://youtube.com/DeputadoNicoletti</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>178986</v>
+        <v>209787</v>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Nilto Tatto</t>
+          <t>Nikolas Ferreira</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>NILTO IGNACIO TATTO</t>
+          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>dep.niltotatto@camara.leg.br</t>
+          <t>dep.nikolasferreira@camara.leg.br</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>@niltotatto</t>
+          <t>@nikolasferreiradm</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/niltotatto</t>
-        </is>
-      </c>
-      <c r="I376" s="2" t="inlineStr"/>
+          <t>https://instagram.com/nikolasferreiradm</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@NikolasFerreiraO</t>
+        </is>
+      </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>194260</v>
+        <v>178986</v>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Nivaldo Albuquerque</t>
+          <t>Nilto Tatto</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>NIVALDO FERREIRA DE ALBUQUERQUE NETO</t>
+          <t>NILTO IGNACIO TATTO</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>dep.nivaldoalbuquerque@camara.leg.br</t>
+          <t>dep.niltotatto@camara.leg.br</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>@nivaldoalbuquerque</t>
+          <t>@niltotatto</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nivaldoalbuquerque</t>
+          <t>https://instagram.com/niltotatto</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr"/>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/194260</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>204498</v>
+        <v>194260</v>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Olival Marques</t>
+          <t>Nivaldo Albuquerque</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
+          <t>NIVALDO FERREIRA DE ALBUQUERQUE NETO</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>dep.olivalmarques@camara.leg.br</t>
+          <t>dep.nivaldoalbuquerque@camara.leg.br</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>@OlivalMarques</t>
+          <t>@nivaldoalbuquerque</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/OlivalMarques</t>
+          <t>https://instagram.com/nivaldoalbuquerque</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/194260</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>178987</v>
+        <v>204498</v>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Orlando Silva</t>
+          <t>Olival Marques</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
+          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>dep.orlandosilva@camara.leg.br</t>
+          <t>dep.olivalmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>@orlandosilvasp</t>
+          <t>@OlivalMarques</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/orlandosilvasp</t>
+          <t>https://instagram.com/OlivalMarques</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr"/>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>73692</v>
+        <v>178987</v>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Osmar Terra</t>
+          <t>Orlando Silva</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>OSMAR GASPARINI TERRA</t>
+          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>dep.osmarterra@camara.leg.br</t>
+          <t>dep.orlandosilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>@terra.osmar</t>
+          <t>@orlandosilvasp</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/terra.osmar</t>
-        </is>
-      </c>
-      <c r="I380" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/orlandosilvasp</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr"/>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>204441</v>
+        <v>73692</v>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Otoni de Paula</t>
+          <t>Osmar Terra</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>OTONI MOURA DE PAULO JUNIOR</t>
+          <t>OSMAR GASPARINI TERRA</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>dep.otonidepaula@camara.leg.br</t>
+          <t>dep.osmarterra@camara.leg.br</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>@otonidepaulaoficial</t>
+          <t>@terra.osmar</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/otonidepaulaoficial</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr"/>
+          <t>https://instagram.com/terra.osmar</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
+        </is>
+      </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>160556</v>
+        <v>204441</v>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Otoni de Paula</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>OTONI MOURA DE PAULO JUNIOR</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.otonidepaula@camara.leg.br</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@otonidepaulaoficial</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/otonidepaulaoficial</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr"/>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>180214</v>
+        <v>160556</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>@pastordiniz.ad</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>160642</v>
+        <v>180214</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G384" s="2" t="inlineStr"/>
-      <c r="H384" s="2" t="inlineStr"/>
+          <t>dep.pastordiniz@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>@pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
       <c r="I384" s="2" t="inlineStr"/>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>204570</v>
+        <v>160642</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G385" s="2" t="inlineStr">
-        <is>
-          <t>@deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr"/>
+      <c r="H385" s="2" t="inlineStr"/>
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>220615</v>
+        <v>204570</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorgil@camara.leg.br</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@deputadogildenemyr</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I386" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>204553</v>
+        <v>220615</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>@pastorsargentoisidorio</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="I387" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>74160</v>
+        <v>204553</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G388" s="2" t="inlineStr"/>
-      <c r="H388" s="2" t="inlineStr"/>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>@pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
       <c r="I388" s="2" t="inlineStr"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>141518</v>
+        <v>74160</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Paulinho da Força</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>PAULO PEREIRA DA SILVA</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.paulinhodaforca@camara.leg.br</t>
+          <t>dep.patrusananias@camara.leg.br</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr"/>
@@ -17602,37 +17602,37 @@
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>141516</v>
+        <v>141518</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Paulo Abi-Ackel</t>
+          <t>Paulinho da Força</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PAULO ABI-ACKEL</t>
+          <t>PAULO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloabiackel@camara.leg.br</t>
+          <t>dep.paulinhodaforca@camara.leg.br</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
@@ -17640,213 +17640,213 @@
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>220650</v>
+        <v>141516</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>Paulo Alexandre Barbosa</t>
+          <t>Paulo Abi-Ackel</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
+          <t>PAULO ABI-ACKEL</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G391" s="2" t="inlineStr">
-        <is>
-          <t>@pauloalexandrebarbosa</t>
-        </is>
-      </c>
-      <c r="H391" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloalexandrebarbosa</t>
-        </is>
-      </c>
+          <t>dep.pauloabiackel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr"/>
+      <c r="H391" s="2" t="inlineStr"/>
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>178860</v>
+        <v>220650</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Paulo Azi</t>
+          <t>Paulo Alexandre Barbosa</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>PAULO VELLOSO DANTAS AZI</t>
+          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloazi@camara.leg.br</t>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>@PauloAziofcial</t>
+          <t>@pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/PauloAziofcial</t>
+          <t>https://instagram.com/pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr"/>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>160517</v>
+        <v>178860</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>Paulo Folletto</t>
+          <t>Paulo Azi</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FOLLETTO</t>
+          <t>PAULO VELLOSO DANTAS AZI</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofolletto@camara.leg.br</t>
+          <t>dep.pauloazi@camara.leg.br</t>
         </is>
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>@paulo.folletto</t>
+          <t>@PauloAziofcial</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/paulo.folletto</t>
+          <t>https://instagram.com/PauloAziofcial</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>160558</v>
+        <v>160517</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Paulo Freire Costa</t>
+          <t>Paulo Folletto</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FREIRE DA COSTA</t>
+          <t>PAULO ROBERTO FOLLETTO</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofreirecosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G394" s="2" t="inlineStr"/>
-      <c r="H394" s="2" t="inlineStr"/>
+          <t>dep.paulofolletto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>@paulo.folletto</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulo.folletto</t>
+        </is>
+      </c>
       <c r="I394" s="2" t="inlineStr"/>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>204492</v>
+        <v>160558</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Paulo Guedes</t>
+          <t>Paulo Freire Costa</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>PAULO JOSE CARLOS GUEDES</t>
+          <t>PAULO ROBERTO FREIRE DA COSTA</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloguedes@camara.leg.br</t>
+          <t>dep.paulofreirecosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
@@ -17854,22 +17854,22 @@
       <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>233592</v>
+        <v>204492</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Paulo Lemos</t>
+          <t>Paulo Guedes</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
+          <t>PAULO JOSE CARLOS GUEDES</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -17879,100 +17879,100 @@
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G396" s="2" t="inlineStr">
-        <is>
-          <t>@paulolemosap</t>
-        </is>
-      </c>
-      <c r="H396" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulolemosap</t>
-        </is>
-      </c>
-      <c r="I396" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
-        </is>
-      </c>
+          <t>dep.pauloguedes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr"/>
+      <c r="H396" s="2" t="inlineStr"/>
+      <c r="I396" s="2" t="inlineStr"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>220685</v>
+        <v>233592</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Paulo Litro</t>
+          <t>Paulo Lemos</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
+          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolitro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr"/>
-      <c r="H397" s="2" t="inlineStr"/>
-      <c r="I397" s="2" t="inlineStr"/>
+          <t>dep.paulolemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>@paulolemosap</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulolemosap</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
+        </is>
+      </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>74574</v>
+        <v>220685</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Paulo Magalhães</t>
+          <t>Paulo Litro</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
+          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomagalhaes@camara.leg.br</t>
+          <t>dep.paulolitro@camara.leg.br</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr"/>
@@ -17980,37 +17980,37 @@
       <c r="I398" s="2" t="inlineStr"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>74400</v>
+        <v>74574</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Paulo Pimenta</t>
+          <t>Paulo Magalhães</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO SEVERO PIMENTA</t>
+          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.paulopimenta@camara.leg.br</t>
+          <t>dep.paulomagalhaes@camara.leg.br</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr"/>
@@ -18018,37 +18018,37 @@
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>154700</v>
+        <v>74400</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Paulo Soares</t>
+          <t>Paulo Pimenta</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
+          <t>PAULO ROBERTO SEVERO PIMENTA</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.paulosoares@camara.leg.br</t>
+          <t>dep.paulopimenta@camara.leg.br</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr"/>
@@ -18056,27 +18056,27 @@
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>141488</v>
+        <v>154700</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Paulo Soares</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -18086,267 +18086,267 @@
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G401" s="2" t="inlineStr">
-        <is>
-          <t>@pauloteixeira13</t>
-        </is>
-      </c>
-      <c r="H401" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloteixeira13</t>
-        </is>
-      </c>
+          <t>dep.paulosoares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr"/>
+      <c r="H401" s="2" t="inlineStr"/>
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>220630</v>
+        <v>141488</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pauloteixeira@camara.leg.br</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pauloteixeira13</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pauloteixeira13</t>
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>220667</v>
+        <v>220630</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>@pedrocampospe</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedrocampospe</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>122974</v>
+        <v>220667</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G404" s="2" t="inlineStr"/>
-      <c r="H404" s="2" t="inlineStr"/>
+          <t>dep.pedrocampos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>@pedrocampospe</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrocampospe</t>
+        </is>
+      </c>
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>204395</v>
+        <v>122974</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G405" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H405" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr"/>
+      <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>122158</v>
+        <v>204395</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G406" s="2" t="inlineStr"/>
-      <c r="H406" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I406" s="2" t="inlineStr"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>160604</v>
+        <v>122158</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedropaulo@camara.leg.br</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr"/>
@@ -18354,37 +18354,37 @@
       <c r="I407" s="2" t="inlineStr"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>204406</v>
+        <v>160604</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr"/>
@@ -18392,206 +18392,206 @@
       <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>161440</v>
+        <v>204406</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G409" s="2" t="inlineStr">
-        <is>
-          <t>@deputadopezenti</t>
-        </is>
-      </c>
-      <c r="H409" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr"/>
+      <c r="H409" s="2" t="inlineStr"/>
       <c r="I409" s="2" t="inlineStr"/>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>204524</v>
+        <v>161440</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pezenti@camara.leg.br</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@deputadopezenti</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
-        </is>
-      </c>
-      <c r="I410" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>73486</v>
+        <v>204524</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>@pompeodemattospdt</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
+          <t>https://instagram.com/pinheirinhomg</t>
         </is>
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/PompeodeMattos</t>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>160601</v>
+        <v>73486</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr"/>
-      <c r="H412" s="2" t="inlineStr"/>
-      <c r="I412" s="2" t="inlineStr"/>
+          <t>dep.pompeodemattos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>@pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PompeodeMattos</t>
+        </is>
+      </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>226075</v>
+        <v>160601</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Priscila Costa</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>PRISCILA BEZERRA DA COSTA</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -18601,449 +18601,449 @@
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.priscilacosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>@priscilacosta</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/priscilacosta</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr"/>
+      <c r="H413" s="2" t="inlineStr"/>
       <c r="I413" s="2" t="inlineStr"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>220533</v>
+        <v>226075</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Priscila Costa</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>PRISCILA BEZERRA DA COSTA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.priscilacosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@priscilacosta</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
-        </is>
-      </c>
+          <t>https://instagram.com/priscilacosta</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>204390</v>
+        <v>220533</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>@professoralcidesoficial</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
+          <t>https://instagram.com/reginaldo.veras</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+          <t>https://youtube.com/Reginaldoveras12</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>221338</v>
+        <v>204390</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr"/>
-      <c r="H416" s="2" t="inlineStr"/>
-      <c r="I416" s="2" t="inlineStr"/>
+          <t>dep.professoralcides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>@professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+        </is>
+      </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>160641</v>
+        <v>221338</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>@profmarcivania</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>220586</v>
+        <v>160641</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
+          <t>dep.professoramarcivania@camara.leg.br</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>@rafaelbrito15</t>
+          <t>@profmarcivania</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I418" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr"/>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>233594</v>
+        <v>220586</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr"/>
-      <c r="H419" s="2" t="inlineStr"/>
-      <c r="I419" s="2" t="inlineStr"/>
+          <t>dep.rafaelbrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>220532</v>
+        <v>233594</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="H420" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr"/>
+      <c r="H420" s="2" t="inlineStr"/>
+      <c r="I420" s="2" t="inlineStr"/>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>220626</v>
+        <v>220532</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
+          <t>dep.rafaelprudente@camara.leg.br</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>@rafaelsimoesmg</t>
+          <t>@rafaelprudentedep</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="I421" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>204567</v>
+        <v>220626</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G422" s="2" t="inlineStr"/>
-      <c r="H422" s="2" t="inlineStr"/>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
       <c r="I422" s="2" t="inlineStr"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>74084</v>
+        <v>204567</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -19053,127 +19053,123 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H423" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I423" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr"/>
+      <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>115200</v>
+        <v>74084</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Raniery Paulino</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.ranierypaulino@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr"/>
-      <c r="H424" s="2" t="inlineStr"/>
-      <c r="I424" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>74161</v>
+        <v>115200</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Raniery Paulino</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.ranierypaulino@camara.leg.br</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr"/>
-      <c r="I425" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I425" s="2" t="inlineStr"/>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>220606</v>
+        <v>74161</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -19183,612 +19179,616 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="2" t="inlineStr"/>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>153423</v>
+        <v>220606</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G427" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H427" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.reimont@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr"/>
+      <c r="H427" s="2" t="inlineStr"/>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>73801</v>
+        <v>153423</v>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr"/>
-      <c r="H428" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I428" s="2" t="inlineStr"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>175765</v>
+        <v>73801</v>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>@ribamarsilvaoficial</t>
-        </is>
-      </c>
-      <c r="H429" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr"/>
       <c r="I429" s="2" t="inlineStr"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>221329</v>
+        <v>175765</v>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Abrão</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MARTINS DAVID</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoabrao@camara.leg.br</t>
+          <t>dep.ribamarsilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>@ricardoabraooficial</t>
+          <t>@ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoabraooficial</t>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr"/>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>220543</v>
+        <v>221329</v>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Ayres</t>
+          <t>Ricardo Abrão</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>RICARDO AYRES DE CARVALHO</t>
+          <t>RICARDO MARTINS DAVID</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoayres@camara.leg.br</t>
+          <t>dep.ricardoabrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>@ricardoayres_to</t>
+          <t>@ricardoabraooficial</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoayres_to</t>
+          <t>https://instagram.com/ricardoabraooficial</t>
         </is>
       </c>
       <c r="I431" s="2" t="inlineStr"/>
       <c r="J431" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>73788</v>
+        <v>220543</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Barros</t>
+          <t>Ricardo Ayres</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
+          <t>RICARDO AYRES DE CARVALHO</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardobarros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr"/>
-      <c r="H432" s="2" t="inlineStr"/>
+          <t>dep.ricardoayres@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>@ricardoayres_to</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardoayres_to</t>
+        </is>
+      </c>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>204362</v>
+        <v>73788</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Guidi</t>
+          <t>Ricardo Barros</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>RICARDO ZANATTA GUIDI</t>
+          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoguidi@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>@ricardozguidi</t>
-        </is>
-      </c>
-      <c r="H433" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardozguidi</t>
-        </is>
-      </c>
+          <t>dep.ricardobarros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr"/>
+      <c r="H433" s="2" t="inlineStr"/>
       <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>220694</v>
+        <v>204362</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Maia</t>
+          <t>Ricardo Guidi</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MAIA CHAVES DE SOUZA</t>
+          <t>RICARDO ZANATTA GUIDI</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardomaia@camara.leg.br</t>
+          <t>dep.ricardoguidi@camara.leg.br</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>@ricardomaia.dabahia</t>
+          <t>@ricardozguidi</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="I434" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/ricardomaiadabahia5610</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ricardozguidi</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr"/>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>220633</v>
+        <v>220694</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Salles</t>
+          <t>Ricardo Maia</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DE AQUINO SALLES</t>
+          <t>RICARDO MAIA CHAVES DE SOUZA</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardosalles@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G435" s="2" t="inlineStr"/>
-      <c r="H435" s="2" t="inlineStr"/>
-      <c r="I435" s="2" t="inlineStr"/>
+          <t>dep.ricardomaia@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>@ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/ricardomaiadabahia5610</t>
+        </is>
+      </c>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>204489</v>
+        <v>220633</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Robério Monteiro</t>
+          <t>Ricardo Salles</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
+          <t>RICARDO DE AQUINO SALLES</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>dep.roberiomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>@dep.roberiomonteiro</t>
-        </is>
-      </c>
-      <c r="H436" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.roberiomonteiro</t>
-        </is>
-      </c>
+          <t>dep.ricardosalles@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr"/>
+      <c r="H436" s="2" t="inlineStr"/>
       <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>220693</v>
+        <v>204489</v>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Roberta Roma</t>
+          <t>Robério Monteiro</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Roberta de Araujo Costa Roma</t>
+          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>dep.robertaroma@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr"/>
-      <c r="H437" s="2" t="inlineStr"/>
+          <t>dep.roberiomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>@dep.roberiomonteiro</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.roberiomonteiro</t>
+        </is>
+      </c>
       <c r="I437" s="2" t="inlineStr"/>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>220588</v>
+        <v>220693</v>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Roberto Duarte</t>
+          <t>Roberta Roma</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO DUARTE JUNIOR</t>
+          <t>Roberta de Araujo Costa Roma</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>dep.robertoduarte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>@rdnarede</t>
-        </is>
-      </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rdnarede</t>
-        </is>
-      </c>
+          <t>dep.robertaroma@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
+      <c r="H438" s="2" t="inlineStr"/>
       <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>220613</v>
+        <v>220588</v>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Roberto Monteiro Pai</t>
+          <t>Roberto Duarte</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
+          <t>ROBERTO DUARTE JUNIOR</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>dep.robertomonteiropai@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr"/>
-      <c r="H439" s="2" t="inlineStr"/>
+          <t>dep.robertoduarte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>@rdnarede</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rdnarede</t>
+        </is>
+      </c>
       <c r="I439" s="2" t="inlineStr"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>220624</v>
+        <v>220613</v>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Robinson Faria</t>
+          <t>Roberto Monteiro Pai</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>ROBINSON MESQUITA DE FARIA</t>
+          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>dep.robinsonfaria@camara.leg.br</t>
+          <t>dep.robertomonteiropai@camara.leg.br</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
@@ -19796,72 +19796,60 @@
       <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>220546</v>
+        <v>220624</v>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Rodolfo Nogueira</t>
+          <t>Robinson Faria</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
+          <t>ROBINSON MESQUITA DE FARIA</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>dep.rodolfonogueira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>@rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="I441" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RodolfoNogueirams</t>
-        </is>
-      </c>
+          <t>dep.robinsonfaria@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr"/>
+      <c r="H441" s="2" t="inlineStr"/>
+      <c r="I441" s="2" t="inlineStr"/>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>230767</v>
+        <v>220546</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo da Zaeli</t>
+          <t>Rodolfo Nogueira</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO LUGLI</t>
+          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -19871,445 +19859,457 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodazaeli@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G442" s="2" t="inlineStr"/>
-      <c r="H442" s="2" t="inlineStr"/>
-      <c r="I442" s="2" t="inlineStr"/>
+          <t>dep.rodolfonogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>@rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RodolfoNogueirams</t>
+        </is>
+      </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>141531</v>
+        <v>230767</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo de Castro</t>
+          <t>Rodrigo da Zaeli</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO BATISTA DE CASTRO</t>
+          <t>RODRIGO LUGLI</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodecastro@camara.leg.br</t>
+          <t>dep.rodrigodazaeli@camara.leg.br</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr"/>
-      <c r="I443" s="2" t="inlineStr">
-        <is>
-          <t>http://www.youtube.com/rodrigocastro45</t>
-        </is>
-      </c>
+      <c r="I443" s="2" t="inlineStr"/>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>220641</v>
+        <v>141531</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Gambale</t>
+          <t>Rodrigo de Castro</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO GAMBALE VIEIRA</t>
+          <t>RODRIGO BATISTA DE CASTRO</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigogambale@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigogambale</t>
-        </is>
-      </c>
-      <c r="H444" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigogambale</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr"/>
+          <t>dep.rodrigodecastro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr"/>
+      <c r="H444" s="2" t="inlineStr"/>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/rodrigocastro45</t>
+        </is>
+      </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>141533</v>
+        <v>220641</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Rollemberg</t>
+          <t>Rodrigo Gambale</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SOBRAL ROLLEMBERG</t>
+          <t>RODRIGO GAMBALE VIEIRA</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigorollemberg@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G445" s="2" t="inlineStr"/>
-      <c r="H445" s="2" t="inlineStr"/>
+          <t>dep.rodrigogambale@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigogambale</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigogambale</t>
+        </is>
+      </c>
       <c r="I445" s="2" t="inlineStr"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>165470</v>
+        <v>141533</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Valadares</t>
+          <t>Rodrigo Rollemberg</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SANTANA VALADARES</t>
+          <t>RODRIGO SOBRAL ROLLEMBERG</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigovaladares@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="H446" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadorodrigovaladares1954</t>
-        </is>
-      </c>
+          <t>dep.rodrigorollemberg@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr"/>
+      <c r="H446" s="2" t="inlineStr"/>
+      <c r="I446" s="2" t="inlineStr"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>220695</v>
+        <v>165470</v>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Rogéria Santos</t>
+          <t>Rodrigo Valadares</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
+          <t>RODRIGO SANTANA VALADARES</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriasantos@camara.leg.br</t>
+          <t>dep.rodrigovaladares@camara.leg.br</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>@rogeriasantosoficial</t>
+          <t>@rodrigovaladares_</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriasantosoficial</t>
+          <t>https://instagram.com/rodrigovaladares_</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
+          <t>https://youtube.com/deputadorodrigovaladares1954</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>204480</v>
+        <v>220695</v>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Rogério Correia</t>
+          <t>Rogéria Santos</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
+          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriocorreia@camara.leg.br</t>
+          <t>dep.rogeriasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>@rogeriocorreia_</t>
+          <t>@rogeriasantosoficial</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriocorreia_</t>
+          <t>https://instagram.com/rogeriasantosoficial</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
+          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>204525</v>
+        <v>204480</v>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Rosana Valle</t>
+          <t>Rogério Correia</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>ROSANA DE OLIVEIRA VALLE</t>
+          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>dep.rosanavalle@camara.leg.br</t>
+          <t>dep.rogeriocorreia@camara.leg.br</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>@rosanavalleoficial</t>
+          <t>@rogeriocorreia_</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosanavalleoficial</t>
+          <t>https://instagram.com/rogeriocorreia_</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>178945</v>
+        <v>204525</v>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Gomes</t>
+          <t>Rosana Valle</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE SOUZA GOMES</t>
+          <t>ROSANA DE OLIVEIRA VALLE</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelagomes@camara.leg.br</t>
+          <t>dep.rosanavalle@camara.leg.br</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>@rosangelasgomes</t>
+          <t>@rosanavalleoficial</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosangelasgomes</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rosanavalleoficial</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+        </is>
+      </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>220644</v>
+        <v>178945</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Moro</t>
+          <t>Rosangela Gomes</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
+          <t>ROSANGELA DE SOUZA GOMES</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelamoro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr"/>
-      <c r="H451" s="2" t="inlineStr"/>
+          <t>dep.rosangelagomes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelasgomes</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelasgomes</t>
+        </is>
+      </c>
       <c r="I451" s="2" t="inlineStr"/>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>220620</v>
+        <v>220644</v>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Rosângela Reis</t>
+          <t>Rosangela Moro</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
+          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -20319,81 +20319,81 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelareis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelareis.mg</t>
-        </is>
-      </c>
-      <c r="H452" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelareis.mg</t>
-        </is>
-      </c>
+          <t>dep.rosangelamoro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr"/>
+      <c r="H452" s="2" t="inlineStr"/>
       <c r="I452" s="2" t="inlineStr"/>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>74371</v>
+        <v>220620</v>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Rubens Otoni</t>
+          <t>Rosângela Reis</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>RUBENS OTONI GOMIDE</t>
+          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>dep.rubensotoni@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G453" s="2" t="inlineStr"/>
-      <c r="H453" s="2" t="inlineStr"/>
+          <t>dep.rosangelareis@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelareis.mg</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelareis.mg</t>
+        </is>
+      </c>
       <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>178887</v>
+        <v>74371</v>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Rubens Pereira Júnior</t>
+          <t>Rubens Otoni</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
+          <t>RUBENS OTONI GOMIDE</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -20403,47 +20403,35 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>dep.rubenspereirajunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>@rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="H454" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
-        </is>
-      </c>
+          <t>dep.rubensotoni@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr"/>
+      <c r="H454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr"/>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>73604</v>
+        <v>178887</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Rui Falcão</t>
+          <t>Rubens Pereira Júnior</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>RUI GOETHE DA COSTA FALCÃO</t>
+          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -20453,286 +20441,298 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>dep.ruifalcao@camara.leg.br</t>
+          <t>dep.rubenspereirajunior@camara.leg.br</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>@ruifalcao13</t>
+          <t>@rubenspereirajr</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruifalcao13</t>
+          <t>https://instagram.com/rubenspereirajr</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/rfalcao13</t>
+          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>160635</v>
+        <v>73604</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Ruy Carneiro</t>
+          <t>Rui Falcão</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
+          <t>RUI GOETHE DA COSTA FALCÃO</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>dep.ruycarneiro@camara.leg.br</t>
+          <t>dep.ruifalcao@camara.leg.br</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>@ruy.carneiro</t>
+          <t>@ruifalcao13</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruy.carneiro</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr"/>
+          <t>https://instagram.com/ruifalcao13</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/rfalcao13</t>
+        </is>
+      </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>204535</v>
+        <v>160635</v>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Sâmia Bomfim</t>
+          <t>Ruy Carneiro</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>SAMIA DE SOUZA BOMFIM</t>
+          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>dep.samiabomfim@camara.leg.br</t>
+          <t>dep.ruycarneiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>@samiabomfim</t>
+          <t>@ruy.carneiro</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/samiabomfim</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/samiabomfimpsol</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ruy.carneiro</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr"/>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>220631</v>
+        <v>204535</v>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Samuel Viana</t>
+          <t>Sâmia Bomfim</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
+          <t>SAMIA DE SOUZA BOMFIM</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>dep.samuelviana@camara.leg.br</t>
+          <t>dep.samiabomfim@camara.leg.br</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>@vianasamuel</t>
+          <t>@samiabomfim</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vianasamuel</t>
+          <t>https://instagram.com/samiabomfim</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
+          <t>https://youtube.com/samiabomfimpsol</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>204416</v>
+        <v>220631</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Samuel Viana</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>UBIRATAN ANTUNES SANDERSON</t>
+          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>dep.sanderson@camara.leg.br</t>
+          <t>dep.samuelviana@camara.leg.br</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>@sandersonrs</t>
+          <t>@vianasamuel</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sandersonrs</t>
+          <t>https://instagram.com/vianasamuel</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>160621</v>
+        <v>204416</v>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Sandro Alex</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
+          <t>UBIRATAN ANTUNES SANDERSON</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>dep.sandroalex@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
-      <c r="I460" s="2" t="inlineStr"/>
+          <t>dep.sanderson@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>@sandersonrs</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sandersonrs</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+        </is>
+      </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>236518</v>
+        <v>160621</v>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Santin Roveda</t>
+          <t>Sandro Alex</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>HILTON SANTIN ROVEDA</t>
+          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -20742,43 +20742,35 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>dep.santinroveda@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>@santinroveda</t>
-        </is>
-      </c>
-      <c r="H461" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/santinroveda</t>
-        </is>
-      </c>
+          <t>dep.sandroalex@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr"/>
+      <c r="H461" s="2" t="inlineStr"/>
       <c r="I461" s="2" t="inlineStr"/>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>204387</v>
+        <v>236518</v>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Sargento Fahur</t>
+          <t>Santin Roveda</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>GILSON CARDOSO FAHUR</t>
+          <t>HILTON SANTIN ROVEDA</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -20788,42 +20780,38 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentofahur@camara.leg.br</t>
+          <t>dep.santinroveda@camara.leg.br</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>@sargentofahurpr</t>
+          <t>@santinroveda</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentofahurpr</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/santinroveda</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr"/>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>220621</v>
+        <v>204387</v>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Sargento Gonçalves</t>
+          <t>Sargento Fahur</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
+          <t>GILSON CARDOSO FAHUR</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -20833,169 +20821,181 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentogoncalves@camara.leg.br</t>
+          <t>dep.sargentofahur@camara.leg.br</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>@sargentogoncalves22</t>
+          <t>@sargentofahurpr</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentogoncalves22</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr"/>
+          <t>https://instagram.com/sargentofahurpr</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
+        </is>
+      </c>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>220618</v>
+        <v>220621</v>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Sargento Portugal</t>
+          <t>Sargento Gonçalves</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ PORTUGAL NETO</t>
+          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentoportugal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G464" s="2" t="inlineStr"/>
-      <c r="H464" s="2" t="inlineStr"/>
+          <t>dep.sargentogoncalves@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>@sargentogoncalves22</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sargentogoncalves22</t>
+        </is>
+      </c>
       <c r="I464" s="2" t="inlineStr"/>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>220713</v>
+        <v>220618</v>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Saullo Vianna</t>
+          <t>Sargento Portugal</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>SAULLO VELAME VIANNA</t>
+          <t>JOSÉ PORTUGAL NETO</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>dep.saullovianna@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G465" s="2" t="inlineStr">
-        <is>
-          <t>@saullovianna</t>
-        </is>
-      </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/saullovianna</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SaulloVianna</t>
-        </is>
-      </c>
+          <t>dep.sargentoportugal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr"/>
+      <c r="H465" s="2" t="inlineStr"/>
+      <c r="I465" s="2" t="inlineStr"/>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>226837</v>
+        <v>220713</v>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>Saulo Pedroso</t>
+          <t>Saullo Vianna</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>SAULO PEDROSO DE SOUZA</t>
+          <t>SAULLO VELAME VIANNA</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>dep.saulopedroso@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G466" s="2" t="inlineStr"/>
-      <c r="H466" s="2" t="inlineStr"/>
-      <c r="I466" s="2" t="inlineStr"/>
+          <t>dep.saullovianna@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>@saullovianna</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/saullovianna</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SaulloVianna</t>
+        </is>
+      </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>73808</v>
+        <v>226837</v>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Brito</t>
+          <t>Saulo Pedroso</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>SÉRGIO LUÍS LACERDA BRITO</t>
+          <t>SAULO PEDROSO DE SOUZA</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -21005,12 +21005,12 @@
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiobrito@camara.leg.br</t>
+          <t>dep.saulopedroso@camara.leg.br</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr"/>
@@ -21018,115 +21018,115 @@
       <c r="I467" s="2" t="inlineStr"/>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>178933</v>
+        <v>73808</v>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Sergio Souza</t>
+          <t>Sérgio Brito</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA</t>
+          <t>SÉRGIO LUÍS LACERDA BRITO</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiosouza@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G468" s="2" t="inlineStr">
-        <is>
-          <t>@sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="H468" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="I468" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadofederalsergiosouza</t>
-        </is>
-      </c>
+          <t>dep.sergiobrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr"/>
+      <c r="H468" s="2" t="inlineStr"/>
+      <c r="I468" s="2" t="inlineStr"/>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>204557</v>
+        <v>178933</v>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Sidney Leite</t>
+          <t>Sergio Souza</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
+          <t>SERGIO DE SOUZA</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>dep.sidneyleite@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G469" s="2" t="inlineStr"/>
-      <c r="H469" s="2" t="inlineStr"/>
-      <c r="I469" s="2" t="inlineStr"/>
+          <t>dep.sergiosouza@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>@sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadofederalsergiosouza</t>
+        </is>
+      </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>74356</v>
+        <v>204557</v>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>Silas Câmara</t>
+          <t>Sidney Leite</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>SILAS CÂMARA</t>
+          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>dep.silascamara@camara.leg.br</t>
+          <t>dep.sidneyleite@camara.leg.br</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr"/>
@@ -21144,37 +21144,37 @@
       <c r="I470" s="2" t="inlineStr"/>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74356</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>204360</v>
+        <v>74356</v>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Silvia Cristina</t>
+          <t>Silas Câmara</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
+          <t>SILAS CÂMARA</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>dep.silviacristina@camara.leg.br</t>
+          <t>dep.silascamara@camara.leg.br</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr"/>
@@ -21182,156 +21182,156 @@
       <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74356</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>204425</v>
+        <v>204360</v>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Silvio Costa Filho</t>
+          <t>Silvia Cristina</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>SILVIO SERAFIM COSTA FILHO</t>
+          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>dep.silviocostafilho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G472" s="2" t="inlineStr">
-        <is>
-          <t>@silviocostafilho</t>
-        </is>
-      </c>
-      <c r="H472" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/silviocostafilho</t>
-        </is>
-      </c>
-      <c r="I472" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SilvioCostaFilhooficial</t>
-        </is>
-      </c>
+          <t>dep.silviacristina@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr"/>
+      <c r="H472" s="2" t="inlineStr"/>
+      <c r="I472" s="2" t="inlineStr"/>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>220569</v>
+        <v>204425</v>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Silvye Alves</t>
+          <t>Silvio Costa Filho</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>SILVYE ALVES DA SILVA</t>
+          <t>SILVIO SERAFIM COSTA FILHO</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>dep.silvyealves@camara.leg.br</t>
+          <t>dep.silviocostafilho@camara.leg.br</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>@silvyealves</t>
+          <t>@silviocostafilho</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/silvyealves</t>
-        </is>
-      </c>
-      <c r="I473" s="2" t="inlineStr"/>
+          <t>https://instagram.com/silviocostafilho</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SilvioCostaFilhooficial</t>
+        </is>
+      </c>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>220651</v>
+        <v>220569</v>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Simone Marquetto</t>
+          <t>Silvye Alves</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
+          <t>SILVYE ALVES DA SILVA</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>dep.simonemarquetto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G474" s="2" t="inlineStr"/>
-      <c r="H474" s="2" t="inlineStr"/>
+          <t>dep.silvyealves@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>@silvyealves</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/silvyealves</t>
+        </is>
+      </c>
       <c r="I474" s="2" t="inlineStr"/>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>104552</v>
+        <v>220651</v>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>Socorro Neri</t>
+          <t>Simone Marquetto</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
+          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -21341,131 +21341,119 @@
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>dep.socorroneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G475" s="2" t="inlineStr">
-        <is>
-          <t>@socorroneri</t>
-        </is>
-      </c>
-      <c r="H475" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/socorroneri</t>
-        </is>
-      </c>
+          <t>dep.simonemarquetto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr"/>
+      <c r="H475" s="2" t="inlineStr"/>
       <c r="I475" s="2" t="inlineStr"/>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>220643</v>
+        <v>104552</v>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>Sônia Guajajara</t>
+          <t>Socorro Neri</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>SONIA BONE DE SOUSA SILVA</t>
+          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>dep.soniaguajajara@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G476" s="2" t="inlineStr"/>
-      <c r="H476" s="2" t="inlineStr"/>
+          <t>dep.socorroneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>@socorroneri</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/socorroneri</t>
+        </is>
+      </c>
       <c r="I476" s="2" t="inlineStr"/>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>178946</v>
+        <v>220643</v>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>Soraya Santos</t>
+          <t>Sônia Guajajara</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>SORAYA ALENCAR DOS SANTOS</t>
+          <t>SONIA BONE DE SOUSA SILVA</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>dep.sorayasantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G477" s="2" t="inlineStr">
-        <is>
-          <t>@dep.sorayasantos</t>
-        </is>
-      </c>
-      <c r="H477" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.sorayasantos</t>
-        </is>
-      </c>
-      <c r="I477" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
-        </is>
-      </c>
+          <t>dep.soniaguajajara@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr"/>
+      <c r="H477" s="2" t="inlineStr"/>
+      <c r="I477" s="2" t="inlineStr"/>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>178947</v>
+        <v>178946</v>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>Sóstenes Cavalcante</t>
+          <t>Soraya Santos</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>SOSTENES SILVA CAVALCANTE</t>
+          <t>SORAYA ALENCAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -21480,191 +21468,203 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>dep.sostenescavalcante@camara.leg.br</t>
+          <t>dep.sorayasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>@sostenescavalcante</t>
+          <t>@dep.sorayasantos</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sostenescavalcante</t>
+          <t>https://instagram.com/dep.sorayasantos</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
+          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>92776</v>
+        <v>178947</v>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Stefano Aguiar</t>
+          <t>Sóstenes Cavalcante</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>STEFANO AGUIAR DOS SANTOS</t>
+          <t>SOSTENES SILVA CAVALCANTE</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>dep.stefanoaguiar@camara.leg.br</t>
+          <t>dep.sostenescavalcante@camara.leg.br</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>@depstefano</t>
+          <t>@sostenescavalcante</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depstefano</t>
-        </is>
-      </c>
-      <c r="I479" s="2" t="inlineStr"/>
+          <t>https://instagram.com/sostenescavalcante</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
+        </is>
+      </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>204534</v>
+        <v>92776</v>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Tabata Amaral</t>
+          <t>Stefano Aguiar</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
+          <t>STEFANO AGUIAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>dep.tabataamaral@camara.leg.br</t>
+          <t>dep.stefanoaguiar@camara.leg.br</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>@tabataamaralsp</t>
+          <t>@depstefano</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="I480" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/depstefano</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr"/>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>220682</v>
+        <v>204534</v>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Tadeu Veneri</t>
+          <t>Tabata Amaral</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO TADEU VENERI</t>
+          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>dep.tadeuveneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G481" s="2" t="inlineStr"/>
-      <c r="H481" s="2" t="inlineStr"/>
-      <c r="I481" s="2" t="inlineStr"/>
+          <t>dep.tabataamaral@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>@tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
+        </is>
+      </c>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>204464</v>
+        <v>220682</v>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>Talíria Petrone</t>
+          <t>Tadeu Veneri</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>TALIRIA PETRONE SOARES</t>
+          <t>ANTONIO TADEU VENERI</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>dep.taliriapetrone@camara.leg.br</t>
+          <t>dep.tadeuveneri@camara.leg.br</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr"/>
@@ -21672,22 +21672,22 @@
       <c r="I482" s="2" t="inlineStr"/>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>220598</v>
+        <v>204464</v>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>Tarcísio Motta</t>
+          <t>Talíria Petrone</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>TARCISIO MOTTA DE CARVALHO</t>
+          <t>TALIRIA PETRONE SOARES</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
@@ -21702,191 +21702,191 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>dep.tarcisiomotta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G483" s="2" t="inlineStr">
-        <is>
-          <t>@tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="H483" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/tarcisiomottapsol</t>
-        </is>
-      </c>
+          <t>dep.taliriapetrone@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr"/>
+      <c r="H483" s="2" t="inlineStr"/>
+      <c r="I483" s="2" t="inlineStr"/>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>220560</v>
+        <v>220598</v>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>Thiago de Joaldo</t>
+          <t>Tarcísio Motta</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>JOSE THIAGO ALVES DE CARVALHO</t>
+          <t>TARCISIO MOTTA DE CARVALHO</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagodejoaldo@camara.leg.br</t>
+          <t>dep.tarcisiomotta@camara.leg.br</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>@thiagodejoaldo</t>
+          <t>@tarcisiomottapsol</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/thiagodejoaldo</t>
-        </is>
-      </c>
-      <c r="I484" s="2" t="inlineStr"/>
+          <t>https://instagram.com/tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/tarcisiomottapsol</t>
+        </is>
+      </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>220597</v>
+        <v>220560</v>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Thiago Flores</t>
+          <t>Thiago de Joaldo</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>THIAGO LEITE FLORES PEREIRA</t>
+          <t>JOSE THIAGO ALVES DE CARVALHO</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagoflores@camara.leg.br</t>
+          <t>dep.thiagodejoaldo@camara.leg.br</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>@deputadothiagoflores</t>
+          <t>@thiagodejoaldo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="I485" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/thiagodejoaldo</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr"/>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>143084</v>
+        <v>220597</v>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas</t>
+          <t>Thiago Flores</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas Braga Pereira</t>
+          <t>THIAGO LEITE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>dep.tiagodimas@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G486" s="2" t="inlineStr"/>
-      <c r="H486" s="2" t="inlineStr"/>
-      <c r="I486" s="2" t="inlineStr"/>
+          <t>dep.thiagoflores@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>@deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
+        </is>
+      </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>220684</v>
+        <v>143084</v>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Tião Medeiros</t>
+          <t>Tiago Dimas</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
+          <t>Tiago Dimas Braga Pereira</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>dep.tiaomedeiros@camara.leg.br</t>
+          <t>dep.tiagodimas@camara.leg.br</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr"/>
@@ -21894,37 +21894,37 @@
       <c r="I487" s="2" t="inlineStr"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>160976</v>
+        <v>220684</v>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Tiririca</t>
+          <t>Tião Medeiros</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
+          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>dep.tiririca@camara.leg.br</t>
+          <t>dep.tiaomedeiros@camara.leg.br</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr"/>
@@ -21932,37 +21932,37 @@
       <c r="I488" s="2" t="inlineStr"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>178934</v>
+        <v>160976</v>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Toninho Wandscheer</t>
+          <t>Tiririca</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO WANDSCHEER</t>
+          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>dep.toninhowandscheer@camara.leg.br</t>
+          <t>dep.tiririca@camara.leg.br</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr"/>
@@ -21970,91 +21970,91 @@
       <c r="I489" s="2" t="inlineStr"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>157130</v>
+        <v>178934</v>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Túlio Gadêlha</t>
+          <t>Toninho Wandscheer</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>TÚLIO GADÊLHA SALES DE MELO</t>
+          <t>ANTONIO WANDSCHEER</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>dep.tuliogadelha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G490" s="2" t="inlineStr">
-        <is>
-          <t>@tulio.gadelha</t>
-        </is>
-      </c>
-      <c r="H490" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tulio.gadelha</t>
-        </is>
-      </c>
+          <t>dep.toninhowandscheer@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr"/>
+      <c r="H490" s="2" t="inlineStr"/>
       <c r="I490" s="2" t="inlineStr"/>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>236423</v>
+        <v>157130</v>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Valdir Trindade</t>
+          <t>Túlio Gadêlha</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>VALDIR TRINDADE DOS SANTOS</t>
+          <t>TÚLIO GADÊLHA SALES DE MELO</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>dep.valdirtrindade@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G491" s="2" t="inlineStr"/>
-      <c r="H491" s="2" t="inlineStr"/>
+          <t>dep.tuliogadelha@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>@tulio.gadelha</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tulio.gadelha</t>
+        </is>
+      </c>
       <c r="I491" s="2" t="inlineStr"/>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -19122,54 +19122,58 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>115200</v>
+        <v>74161</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Raniery Paulino</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.ranierypaulino@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr"/>
-      <c r="I425" s="2" t="inlineStr"/>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>74161</v>
+        <v>220606</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -19179,616 +19183,612 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.reimont@camara.leg.br</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I426" s="2" t="inlineStr"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>220606</v>
+        <v>153423</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G427" s="2" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>153423</v>
+        <v>73801</v>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>73801</v>
+        <v>175765</v>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr"/>
-      <c r="H429" s="2" t="inlineStr"/>
+          <t>dep.ribamarsilva@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>@ribamarsilvaoficial</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
+        </is>
+      </c>
       <c r="I429" s="2" t="inlineStr"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>175765</v>
+        <v>221329</v>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Ricardo Abrão</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>RICARDO MARTINS DAVID</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
+          <t>dep.ricardoabrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>@ribamarsilvaoficial</t>
+          <t>@ricardoabraooficial</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
+          <t>https://instagram.com/ricardoabraooficial</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr"/>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>221329</v>
+        <v>220543</v>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Abrão</t>
+          <t>Ricardo Ayres</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MARTINS DAVID</t>
+          <t>RICARDO AYRES DE CARVALHO</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoabrao@camara.leg.br</t>
+          <t>dep.ricardoayres@camara.leg.br</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>@ricardoabraooficial</t>
+          <t>@ricardoayres_to</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoabraooficial</t>
+          <t>https://instagram.com/ricardoayres_to</t>
         </is>
       </c>
       <c r="I431" s="2" t="inlineStr"/>
       <c r="J431" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>220543</v>
+        <v>73788</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Ayres</t>
+          <t>Ricardo Barros</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>RICARDO AYRES DE CARVALHO</t>
+          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoayres@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>@ricardoayres_to</t>
-        </is>
-      </c>
-      <c r="H432" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardoayres_to</t>
-        </is>
-      </c>
+          <t>dep.ricardobarros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr"/>
+      <c r="H432" s="2" t="inlineStr"/>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>73788</v>
+        <v>204362</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Barros</t>
+          <t>Ricardo Guidi</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
+          <t>RICARDO ZANATTA GUIDI</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardobarros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G433" s="2" t="inlineStr"/>
-      <c r="H433" s="2" t="inlineStr"/>
+          <t>dep.ricardoguidi@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>@ricardozguidi</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardozguidi</t>
+        </is>
+      </c>
       <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>204362</v>
+        <v>220694</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Guidi</t>
+          <t>Ricardo Maia</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>RICARDO ZANATTA GUIDI</t>
+          <t>RICARDO MAIA CHAVES DE SOUZA</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoguidi@camara.leg.br</t>
+          <t>dep.ricardomaia@camara.leg.br</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>@ricardozguidi</t>
+          <t>@ricardomaia.dabahia</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardozguidi</t>
-        </is>
-      </c>
-      <c r="I434" s="2" t="inlineStr"/>
+          <t>https://instagram.com/ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/ricardomaiadabahia5610</t>
+        </is>
+      </c>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>220694</v>
+        <v>220633</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Maia</t>
+          <t>Ricardo Salles</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MAIA CHAVES DE SOUZA</t>
+          <t>RICARDO DE AQUINO SALLES</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardomaia@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>@ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="H435" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="I435" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/ricardomaiadabahia5610</t>
-        </is>
-      </c>
+          <t>dep.ricardosalles@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr"/>
+      <c r="H435" s="2" t="inlineStr"/>
+      <c r="I435" s="2" t="inlineStr"/>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>220633</v>
+        <v>204489</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Salles</t>
+          <t>Robério Monteiro</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DE AQUINO SALLES</t>
+          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardosalles@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr"/>
-      <c r="H436" s="2" t="inlineStr"/>
+          <t>dep.roberiomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>@dep.roberiomonteiro</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.roberiomonteiro</t>
+        </is>
+      </c>
       <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>204489</v>
+        <v>220693</v>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Robério Monteiro</t>
+          <t>Roberta Roma</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
+          <t>Roberta de Araujo Costa Roma</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>dep.roberiomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>@dep.roberiomonteiro</t>
-        </is>
-      </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.roberiomonteiro</t>
-        </is>
-      </c>
+          <t>dep.robertaroma@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr"/>
+      <c r="H437" s="2" t="inlineStr"/>
       <c r="I437" s="2" t="inlineStr"/>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>220693</v>
+        <v>220588</v>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Roberta Roma</t>
+          <t>Roberto Duarte</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Roberta de Araujo Costa Roma</t>
+          <t>ROBERTO DUARTE JUNIOR</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>dep.robertaroma@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr"/>
-      <c r="H438" s="2" t="inlineStr"/>
+          <t>dep.robertoduarte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>@rdnarede</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rdnarede</t>
+        </is>
+      </c>
       <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>220588</v>
+        <v>220613</v>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Roberto Duarte</t>
+          <t>Roberto Monteiro Pai</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO DUARTE JUNIOR</t>
+          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>dep.robertoduarte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>@rdnarede</t>
-        </is>
-      </c>
-      <c r="H439" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rdnarede</t>
-        </is>
-      </c>
+          <t>dep.robertomonteiropai@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr"/>
+      <c r="H439" s="2" t="inlineStr"/>
       <c r="I439" s="2" t="inlineStr"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>220613</v>
+        <v>220624</v>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Roberto Monteiro Pai</t>
+          <t>Robinson Faria</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
+          <t>ROBINSON MESQUITA DE FARIA</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>dep.robertomonteiropai@camara.leg.br</t>
+          <t>dep.robinsonfaria@camara.leg.br</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
@@ -19796,60 +19796,72 @@
       <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>220624</v>
+        <v>220546</v>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Robinson Faria</t>
+          <t>Rodolfo Nogueira</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>ROBINSON MESQUITA DE FARIA</t>
+          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>dep.robinsonfaria@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr"/>
-      <c r="H441" s="2" t="inlineStr"/>
-      <c r="I441" s="2" t="inlineStr"/>
+          <t>dep.rodolfonogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>@rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RodolfoNogueirams</t>
+        </is>
+      </c>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>220546</v>
+        <v>230767</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Rodolfo Nogueira</t>
+          <t>Rodrigo da Zaeli</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
+          <t>RODRIGO LUGLI</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -19859,457 +19871,445 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>dep.rodolfonogueira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>@rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="H442" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="I442" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RodolfoNogueirams</t>
-        </is>
-      </c>
+          <t>dep.rodrigodazaeli@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr"/>
+      <c r="H442" s="2" t="inlineStr"/>
+      <c r="I442" s="2" t="inlineStr"/>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>230767</v>
+        <v>141531</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo da Zaeli</t>
+          <t>Rodrigo de Castro</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO LUGLI</t>
+          <t>RODRIGO BATISTA DE CASTRO</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodazaeli@camara.leg.br</t>
+          <t>dep.rodrigodecastro@camara.leg.br</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr"/>
-      <c r="I443" s="2" t="inlineStr"/>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/rodrigocastro45</t>
+        </is>
+      </c>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>141531</v>
+        <v>220641</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo de Castro</t>
+          <t>Rodrigo Gambale</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO BATISTA DE CASTRO</t>
+          <t>RODRIGO GAMBALE VIEIRA</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodecastro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr"/>
-      <c r="H444" s="2" t="inlineStr"/>
-      <c r="I444" s="2" t="inlineStr">
-        <is>
-          <t>http://www.youtube.com/rodrigocastro45</t>
-        </is>
-      </c>
+          <t>dep.rodrigogambale@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigogambale</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigogambale</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>220641</v>
+        <v>141533</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Gambale</t>
+          <t>Rodrigo Rollemberg</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO GAMBALE VIEIRA</t>
+          <t>RODRIGO SOBRAL ROLLEMBERG</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigogambale@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigogambale</t>
-        </is>
-      </c>
-      <c r="H445" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigogambale</t>
-        </is>
-      </c>
+          <t>dep.rodrigorollemberg@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr"/>
+      <c r="H445" s="2" t="inlineStr"/>
       <c r="I445" s="2" t="inlineStr"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>141533</v>
+        <v>165470</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Rollemberg</t>
+          <t>Rodrigo Valadares</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SOBRAL ROLLEMBERG</t>
+          <t>RODRIGO SANTANA VALADARES</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigorollemberg@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G446" s="2" t="inlineStr"/>
-      <c r="H446" s="2" t="inlineStr"/>
-      <c r="I446" s="2" t="inlineStr"/>
+          <t>dep.rodrigovaladares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigovaladares_</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigovaladares_</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadorodrigovaladares1954</t>
+        </is>
+      </c>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>165470</v>
+        <v>220695</v>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Valadares</t>
+          <t>Rogéria Santos</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SANTANA VALADARES</t>
+          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigovaladares@camara.leg.br</t>
+          <t>dep.rogeriasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>@rodrigovaladares_</t>
+          <t>@rogeriasantosoficial</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rodrigovaladares_</t>
+          <t>https://instagram.com/rogeriasantosoficial</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/deputadorodrigovaladares1954</t>
+          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>220695</v>
+        <v>204480</v>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Rogéria Santos</t>
+          <t>Rogério Correia</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
+          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriasantos@camara.leg.br</t>
+          <t>dep.rogeriocorreia@camara.leg.br</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>@rogeriasantosoficial</t>
+          <t>@rogeriocorreia_</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriasantosoficial</t>
+          <t>https://instagram.com/rogeriocorreia_</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
+          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>204480</v>
+        <v>204525</v>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Rogério Correia</t>
+          <t>Rosana Valle</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
+          <t>ROSANA DE OLIVEIRA VALLE</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriocorreia@camara.leg.br</t>
+          <t>dep.rosanavalle@camara.leg.br</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>@rogeriocorreia_</t>
+          <t>@rosanavalleoficial</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriocorreia_</t>
+          <t>https://instagram.com/rosanavalleoficial</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
+          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>204525</v>
+        <v>178945</v>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Rosana Valle</t>
+          <t>Rosangela Gomes</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>ROSANA DE OLIVEIRA VALLE</t>
+          <t>ROSANGELA DE SOUZA GOMES</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>dep.rosanavalle@camara.leg.br</t>
+          <t>dep.rosangelagomes@camara.leg.br</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>@rosanavalleoficial</t>
+          <t>@rosangelasgomes</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosanavalleoficial</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rosangelasgomes</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr"/>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>178945</v>
+        <v>220644</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Gomes</t>
+          <t>Rosangela Moro</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE SOUZA GOMES</t>
+          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelagomes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelasgomes</t>
-        </is>
-      </c>
-      <c r="H451" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelasgomes</t>
-        </is>
-      </c>
+          <t>dep.rosangelamoro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr"/>
+      <c r="H451" s="2" t="inlineStr"/>
       <c r="I451" s="2" t="inlineStr"/>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>220644</v>
+        <v>220620</v>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Moro</t>
+          <t>Rosângela Reis</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
+          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -20319,81 +20319,81 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelamoro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G452" s="2" t="inlineStr"/>
-      <c r="H452" s="2" t="inlineStr"/>
+          <t>dep.rosangelareis@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelareis.mg</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelareis.mg</t>
+        </is>
+      </c>
       <c r="I452" s="2" t="inlineStr"/>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>220620</v>
+        <v>74371</v>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Rosângela Reis</t>
+          <t>Rubens Otoni</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
+          <t>RUBENS OTONI GOMIDE</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelareis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelareis.mg</t>
-        </is>
-      </c>
-      <c r="H453" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelareis.mg</t>
-        </is>
-      </c>
+          <t>dep.rubensotoni@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr"/>
+      <c r="H453" s="2" t="inlineStr"/>
       <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>74371</v>
+        <v>178887</v>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Rubens Otoni</t>
+          <t>Rubens Pereira Júnior</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>RUBENS OTONI GOMIDE</t>
+          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -20403,35 +20403,47 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>dep.rubensotoni@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G454" s="2" t="inlineStr"/>
-      <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="2" t="inlineStr"/>
+          <t>dep.rubenspereirajunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>@rubenspereirajr</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rubenspereirajr</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>178887</v>
+        <v>73604</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Rubens Pereira Júnior</t>
+          <t>Rui Falcão</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
+          <t>RUI GOETHE DA COSTA FALCÃO</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -20441,298 +20453,286 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>dep.rubenspereirajunior@camara.leg.br</t>
+          <t>dep.ruifalcao@camara.leg.br</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>@rubenspereirajr</t>
+          <t>@ruifalcao13</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rubenspereirajr</t>
+          <t>https://instagram.com/ruifalcao13</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
+          <t>https://youtube.com/rfalcao13</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>73604</v>
+        <v>160635</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Rui Falcão</t>
+          <t>Ruy Carneiro</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>RUI GOETHE DA COSTA FALCÃO</t>
+          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>dep.ruifalcao@camara.leg.br</t>
+          <t>dep.ruycarneiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>@ruifalcao13</t>
+          <t>@ruy.carneiro</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruifalcao13</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/rfalcao13</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ruy.carneiro</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr"/>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>160635</v>
+        <v>204535</v>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Ruy Carneiro</t>
+          <t>Sâmia Bomfim</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
+          <t>SAMIA DE SOUZA BOMFIM</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>dep.ruycarneiro@camara.leg.br</t>
+          <t>dep.samiabomfim@camara.leg.br</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>@ruy.carneiro</t>
+          <t>@samiabomfim</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruy.carneiro</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr"/>
+          <t>https://instagram.com/samiabomfim</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/samiabomfimpsol</t>
+        </is>
+      </c>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>204535</v>
+        <v>220631</v>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Sâmia Bomfim</t>
+          <t>Samuel Viana</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>SAMIA DE SOUZA BOMFIM</t>
+          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>dep.samiabomfim@camara.leg.br</t>
+          <t>dep.samuelviana@camara.leg.br</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>@samiabomfim</t>
+          <t>@vianasamuel</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/samiabomfim</t>
+          <t>https://instagram.com/vianasamuel</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/samiabomfimpsol</t>
+          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>220631</v>
+        <v>204416</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Samuel Viana</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
+          <t>UBIRATAN ANTUNES SANDERSON</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>dep.samuelviana@camara.leg.br</t>
+          <t>dep.sanderson@camara.leg.br</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>@vianasamuel</t>
+          <t>@sandersonrs</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vianasamuel</t>
+          <t>https://instagram.com/sandersonrs</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
+          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>204416</v>
+        <v>160621</v>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Sandro Alex</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>UBIRATAN ANTUNES SANDERSON</t>
+          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>dep.sanderson@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>@sandersonrs</t>
-        </is>
-      </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sandersonrs</t>
-        </is>
-      </c>
-      <c r="I460" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
-        </is>
-      </c>
+          <t>dep.sandroalex@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr"/>
+      <c r="H460" s="2" t="inlineStr"/>
+      <c r="I460" s="2" t="inlineStr"/>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>160621</v>
+        <v>236518</v>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Sandro Alex</t>
+          <t>Santin Roveda</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
+          <t>HILTON SANTIN ROVEDA</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -20742,35 +20742,43 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>dep.sandroalex@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr"/>
-      <c r="H461" s="2" t="inlineStr"/>
+          <t>dep.santinroveda@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>@santinroveda</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/santinroveda</t>
+        </is>
+      </c>
       <c r="I461" s="2" t="inlineStr"/>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>236518</v>
+        <v>204387</v>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Santin Roveda</t>
+          <t>Sargento Fahur</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>HILTON SANTIN ROVEDA</t>
+          <t>GILSON CARDOSO FAHUR</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -20780,38 +20788,42 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>dep.santinroveda@camara.leg.br</t>
+          <t>dep.sargentofahur@camara.leg.br</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>@santinroveda</t>
+          <t>@sargentofahurpr</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/santinroveda</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="inlineStr"/>
+          <t>https://instagram.com/sargentofahurpr</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
+        </is>
+      </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>204387</v>
+        <v>220621</v>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Sargento Fahur</t>
+          <t>Sargento Gonçalves</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>GILSON CARDOSO FAHUR</t>
+          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -20821,181 +20833,169 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentofahur@camara.leg.br</t>
+          <t>dep.sargentogoncalves@camara.leg.br</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>@sargentofahurpr</t>
+          <t>@sargentogoncalves22</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentofahurpr</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/sargentogoncalves22</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr"/>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>220621</v>
+        <v>220618</v>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Sargento Gonçalves</t>
+          <t>Sargento Portugal</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
+          <t>JOSÉ PORTUGAL NETO</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentogoncalves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G464" s="2" t="inlineStr">
-        <is>
-          <t>@sargentogoncalves22</t>
-        </is>
-      </c>
-      <c r="H464" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sargentogoncalves22</t>
-        </is>
-      </c>
+          <t>dep.sargentoportugal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr"/>
+      <c r="H464" s="2" t="inlineStr"/>
       <c r="I464" s="2" t="inlineStr"/>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>220618</v>
+        <v>220713</v>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Sargento Portugal</t>
+          <t>Saullo Vianna</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ PORTUGAL NETO</t>
+          <t>SAULLO VELAME VIANNA</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentoportugal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G465" s="2" t="inlineStr"/>
-      <c r="H465" s="2" t="inlineStr"/>
-      <c r="I465" s="2" t="inlineStr"/>
+          <t>dep.saullovianna@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>@saullovianna</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/saullovianna</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SaulloVianna</t>
+        </is>
+      </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>220713</v>
+        <v>226837</v>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>Saullo Vianna</t>
+          <t>Saulo Pedroso</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>SAULLO VELAME VIANNA</t>
+          <t>SAULO PEDROSO DE SOUZA</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>dep.saullovianna@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G466" s="2" t="inlineStr">
-        <is>
-          <t>@saullovianna</t>
-        </is>
-      </c>
-      <c r="H466" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/saullovianna</t>
-        </is>
-      </c>
-      <c r="I466" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SaulloVianna</t>
-        </is>
-      </c>
+          <t>dep.saulopedroso@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr"/>
+      <c r="H466" s="2" t="inlineStr"/>
+      <c r="I466" s="2" t="inlineStr"/>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>226837</v>
+        <v>73808</v>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>Saulo Pedroso</t>
+          <t>Sérgio Brito</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>SAULO PEDROSO DE SOUZA</t>
+          <t>SÉRGIO LUÍS LACERDA BRITO</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -21005,12 +21005,12 @@
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>dep.saulopedroso@camara.leg.br</t>
+          <t>dep.sergiobrito@camara.leg.br</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr"/>
@@ -21018,115 +21018,115 @@
       <c r="I467" s="2" t="inlineStr"/>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>73808</v>
+        <v>178933</v>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Brito</t>
+          <t>Sergio Souza</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>SÉRGIO LUÍS LACERDA BRITO</t>
+          <t>SERGIO DE SOUZA</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiobrito@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G468" s="2" t="inlineStr"/>
-      <c r="H468" s="2" t="inlineStr"/>
-      <c r="I468" s="2" t="inlineStr"/>
+          <t>dep.sergiosouza@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>@sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadofederalsergiosouza</t>
+        </is>
+      </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>178933</v>
+        <v>204557</v>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Sergio Souza</t>
+          <t>Sidney Leite</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA</t>
+          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiosouza@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G469" s="2" t="inlineStr">
-        <is>
-          <t>@sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="H469" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="I469" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadofederalsergiosouza</t>
-        </is>
-      </c>
+          <t>dep.sidneyleite@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr"/>
+      <c r="H469" s="2" t="inlineStr"/>
+      <c r="I469" s="2" t="inlineStr"/>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>204557</v>
+        <v>74356</v>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>Sidney Leite</t>
+          <t>Silas Câmara</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
+          <t>SILAS CÂMARA</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>dep.sidneyleite@camara.leg.br</t>
+          <t>dep.silascamara@camara.leg.br</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr"/>
@@ -21144,37 +21144,37 @@
       <c r="I470" s="2" t="inlineStr"/>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74356</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>74356</v>
+        <v>204360</v>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Silas Câmara</t>
+          <t>Silvia Cristina</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>SILAS CÂMARA</t>
+          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>dep.silascamara@camara.leg.br</t>
+          <t>dep.silviacristina@camara.leg.br</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr"/>
@@ -21182,156 +21182,156 @@
       <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74356</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>204360</v>
+        <v>204425</v>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Silvia Cristina</t>
+          <t>Silvio Costa Filho</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
+          <t>SILVIO SERAFIM COSTA FILHO</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>dep.silviacristina@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G472" s="2" t="inlineStr"/>
-      <c r="H472" s="2" t="inlineStr"/>
-      <c r="I472" s="2" t="inlineStr"/>
+          <t>dep.silviocostafilho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>@silviocostafilho</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/silviocostafilho</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SilvioCostaFilhooficial</t>
+        </is>
+      </c>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>204425</v>
+        <v>220569</v>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Silvio Costa Filho</t>
+          <t>Silvye Alves</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>SILVIO SERAFIM COSTA FILHO</t>
+          <t>SILVYE ALVES DA SILVA</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>dep.silviocostafilho@camara.leg.br</t>
+          <t>dep.silvyealves@camara.leg.br</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>@silviocostafilho</t>
+          <t>@silvyealves</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/silviocostafilho</t>
-        </is>
-      </c>
-      <c r="I473" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SilvioCostaFilhooficial</t>
-        </is>
-      </c>
+          <t>https://instagram.com/silvyealves</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr"/>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>220569</v>
+        <v>220651</v>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Silvye Alves</t>
+          <t>Simone Marquetto</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>SILVYE ALVES DA SILVA</t>
+          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>dep.silvyealves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G474" s="2" t="inlineStr">
-        <is>
-          <t>@silvyealves</t>
-        </is>
-      </c>
-      <c r="H474" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/silvyealves</t>
-        </is>
-      </c>
+          <t>dep.simonemarquetto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr"/>
+      <c r="H474" s="2" t="inlineStr"/>
       <c r="I474" s="2" t="inlineStr"/>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>220651</v>
+        <v>104552</v>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>Simone Marquetto</t>
+          <t>Socorro Neri</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
+          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -21341,119 +21341,131 @@
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>dep.simonemarquetto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G475" s="2" t="inlineStr"/>
-      <c r="H475" s="2" t="inlineStr"/>
+          <t>dep.socorroneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>@socorroneri</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/socorroneri</t>
+        </is>
+      </c>
       <c r="I475" s="2" t="inlineStr"/>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>104552</v>
+        <v>220643</v>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>Socorro Neri</t>
+          <t>Sônia Guajajara</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
+          <t>SONIA BONE DE SOUSA SILVA</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>dep.socorroneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G476" s="2" t="inlineStr">
-        <is>
-          <t>@socorroneri</t>
-        </is>
-      </c>
-      <c r="H476" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/socorroneri</t>
-        </is>
-      </c>
+          <t>dep.soniaguajajara@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr"/>
+      <c r="H476" s="2" t="inlineStr"/>
       <c r="I476" s="2" t="inlineStr"/>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>220643</v>
+        <v>178946</v>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>Sônia Guajajara</t>
+          <t>Soraya Santos</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>SONIA BONE DE SOUSA SILVA</t>
+          <t>SORAYA ALENCAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>dep.soniaguajajara@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G477" s="2" t="inlineStr"/>
-      <c r="H477" s="2" t="inlineStr"/>
-      <c r="I477" s="2" t="inlineStr"/>
+          <t>dep.sorayasantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>@dep.sorayasantos</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.sorayasantos</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
+        </is>
+      </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>178946</v>
+        <v>178947</v>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>Soraya Santos</t>
+          <t>Sóstenes Cavalcante</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>SORAYA ALENCAR DOS SANTOS</t>
+          <t>SOSTENES SILVA CAVALCANTE</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -21468,203 +21480,191 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>dep.sorayasantos@camara.leg.br</t>
+          <t>dep.sostenescavalcante@camara.leg.br</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>@dep.sorayasantos</t>
+          <t>@sostenescavalcante</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep.sorayasantos</t>
+          <t>https://instagram.com/sostenescavalcante</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
+          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>178947</v>
+        <v>92776</v>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Sóstenes Cavalcante</t>
+          <t>Stefano Aguiar</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>SOSTENES SILVA CAVALCANTE</t>
+          <t>STEFANO AGUIAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>dep.sostenescavalcante@camara.leg.br</t>
+          <t>dep.stefanoaguiar@camara.leg.br</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>@sostenescavalcante</t>
+          <t>@depstefano</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sostenescavalcante</t>
-        </is>
-      </c>
-      <c r="I479" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/depstefano</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr"/>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>92776</v>
+        <v>204534</v>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Stefano Aguiar</t>
+          <t>Tabata Amaral</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>STEFANO AGUIAR DOS SANTOS</t>
+          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>dep.stefanoaguiar@camara.leg.br</t>
+          <t>dep.tabataamaral@camara.leg.br</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>@depstefano</t>
+          <t>@tabataamaralsp</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depstefano</t>
-        </is>
-      </c>
-      <c r="I480" s="2" t="inlineStr"/>
+          <t>https://instagram.com/tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
+        </is>
+      </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>204534</v>
+        <v>220682</v>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Tabata Amaral</t>
+          <t>Tadeu Veneri</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
+          <t>ANTONIO TADEU VENERI</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>dep.tabataamaral@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G481" s="2" t="inlineStr">
-        <is>
-          <t>@tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="H481" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="I481" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
-        </is>
-      </c>
+          <t>dep.tadeuveneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr"/>
+      <c r="H481" s="2" t="inlineStr"/>
+      <c r="I481" s="2" t="inlineStr"/>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>220682</v>
+        <v>204464</v>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>Tadeu Veneri</t>
+          <t>Talíria Petrone</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO TADEU VENERI</t>
+          <t>TALIRIA PETRONE SOARES</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>dep.tadeuveneri@camara.leg.br</t>
+          <t>dep.taliriapetrone@camara.leg.br</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr"/>
@@ -21672,22 +21672,22 @@
       <c r="I482" s="2" t="inlineStr"/>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>204464</v>
+        <v>220598</v>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>Talíria Petrone</t>
+          <t>Tarcísio Motta</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>TALIRIA PETRONE SOARES</t>
+          <t>TARCISIO MOTTA DE CARVALHO</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
@@ -21702,191 +21702,191 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>dep.taliriapetrone@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G483" s="2" t="inlineStr"/>
-      <c r="H483" s="2" t="inlineStr"/>
-      <c r="I483" s="2" t="inlineStr"/>
+          <t>dep.tarcisiomotta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>@tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/tarcisiomottapsol</t>
+        </is>
+      </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>220598</v>
+        <v>220560</v>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>Tarcísio Motta</t>
+          <t>Thiago de Joaldo</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>TARCISIO MOTTA DE CARVALHO</t>
+          <t>JOSE THIAGO ALVES DE CARVALHO</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>dep.tarcisiomotta@camara.leg.br</t>
+          <t>dep.thiagodejoaldo@camara.leg.br</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>@tarcisiomottapsol</t>
+          <t>@thiagodejoaldo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="I484" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/tarcisiomottapsol</t>
-        </is>
-      </c>
+          <t>https://instagram.com/thiagodejoaldo</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr"/>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>220560</v>
+        <v>220597</v>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Thiago de Joaldo</t>
+          <t>Thiago Flores</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>JOSE THIAGO ALVES DE CARVALHO</t>
+          <t>THIAGO LEITE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagodejoaldo@camara.leg.br</t>
+          <t>dep.thiagoflores@camara.leg.br</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>@thiagodejoaldo</t>
+          <t>@deputadothiagoflores</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/thiagodejoaldo</t>
-        </is>
-      </c>
-      <c r="I485" s="2" t="inlineStr"/>
+          <t>https://instagram.com/deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
+        </is>
+      </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>220597</v>
+        <v>143084</v>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Thiago Flores</t>
+          <t>Tiago Dimas</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>THIAGO LEITE FLORES PEREIRA</t>
+          <t>Tiago Dimas Braga Pereira</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagoflores@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G486" s="2" t="inlineStr">
-        <is>
-          <t>@deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="H486" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="I486" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
-        </is>
-      </c>
+          <t>dep.tiagodimas@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr"/>
+      <c r="H486" s="2" t="inlineStr"/>
+      <c r="I486" s="2" t="inlineStr"/>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>143084</v>
+        <v>220684</v>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas</t>
+          <t>Tião Medeiros</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas Braga Pereira</t>
+          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>dep.tiagodimas@camara.leg.br</t>
+          <t>dep.tiaomedeiros@camara.leg.br</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr"/>
@@ -21894,37 +21894,37 @@
       <c r="I487" s="2" t="inlineStr"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>220684</v>
+        <v>160976</v>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Tião Medeiros</t>
+          <t>Tiririca</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
+          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>dep.tiaomedeiros@camara.leg.br</t>
+          <t>dep.tiririca@camara.leg.br</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr"/>
@@ -21932,37 +21932,37 @@
       <c r="I488" s="2" t="inlineStr"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>160976</v>
+        <v>178934</v>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Tiririca</t>
+          <t>Toninho Wandscheer</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
+          <t>ANTONIO WANDSCHEER</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>dep.tiririca@camara.leg.br</t>
+          <t>dep.toninhowandscheer@camara.leg.br</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr"/>
@@ -21970,106 +21970,106 @@
       <c r="I489" s="2" t="inlineStr"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>178934</v>
+        <v>157130</v>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Toninho Wandscheer</t>
+          <t>Túlio Gadêlha</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO WANDSCHEER</t>
+          <t>TÚLIO GADÊLHA SALES DE MELO</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>dep.toninhowandscheer@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G490" s="2" t="inlineStr"/>
-      <c r="H490" s="2" t="inlineStr"/>
+          <t>dep.tuliogadelha@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>@tulio.gadelha</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tulio.gadelha</t>
+        </is>
+      </c>
       <c r="I490" s="2" t="inlineStr"/>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>157130</v>
+        <v>160610</v>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Túlio Gadêlha</t>
+          <t>Valmir Assunção</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>TÚLIO GADÊLHA SALES DE MELO</t>
+          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>dep.tuliogadelha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>@tulio.gadelha</t>
-        </is>
-      </c>
-      <c r="H491" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tulio.gadelha</t>
-        </is>
-      </c>
+          <t>dep.valmirassuncao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr"/>
+      <c r="H491" s="2" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr"/>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>160610</v>
+        <v>74376</v>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>Valmir Assunção</t>
+          <t>Vander Loubet</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
+          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -22079,165 +22079,177 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>dep.valmirassuncao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G492" s="2" t="inlineStr"/>
-      <c r="H492" s="2" t="inlineStr"/>
+          <t>dep.vanderloubet@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>@vanderloubet</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vanderloubet</t>
+        </is>
+      </c>
       <c r="I492" s="2" t="inlineStr"/>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>74376</v>
+        <v>204396</v>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>Vander Loubet</t>
+          <t>Vermelho</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
+          <t>NELSI COGUETTO MARIA</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>dep.vanderloubet@camara.leg.br</t>
+          <t>dep.vermelho@camara.leg.br</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>@vanderloubet</t>
+          <t>@deputado_vermelho</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vanderloubet</t>
+          <t>https://instagram.com/deputado_vermelho</t>
         </is>
       </c>
       <c r="I493" s="2" t="inlineStr"/>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>204396</v>
+        <v>137070</v>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>Vermelho</t>
+          <t>Vicentinho Júnior</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>NELSI COGUETTO MARIA</t>
+          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>dep.vermelho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>@deputado_vermelho</t>
-        </is>
-      </c>
-      <c r="H494" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputado_vermelho</t>
-        </is>
-      </c>
+          <t>dep.vicentinhojunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr"/>
+      <c r="H494" s="2" t="inlineStr"/>
       <c r="I494" s="2" t="inlineStr"/>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>137070</v>
+        <v>141555</v>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>Vicentinho Júnior</t>
+          <t>Vinicius Carvalho</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
+          <t>VINICIUS RAPOZO DE CARVALHO</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>dep.vicentinhojunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G495" s="2" t="inlineStr"/>
-      <c r="H495" s="2" t="inlineStr"/>
-      <c r="I495" s="2" t="inlineStr"/>
+          <t>dep.viniciuscarvalho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>@viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
+        </is>
+      </c>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>141555</v>
+        <v>160591</v>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Carvalho</t>
+          <t>Vinicius Gurgel</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS RAPOZO DE CARVALHO</t>
+          <t>VINICIUS DE AZEVEDO GURGEL</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -22247,215 +22259,211 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciuscarvalho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G496" s="2" t="inlineStr">
-        <is>
-          <t>@viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="H496" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="I496" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
-        </is>
-      </c>
+          <t>dep.viniciusgurgel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr"/>
+      <c r="H496" s="2" t="inlineStr"/>
+      <c r="I496" s="2" t="inlineStr"/>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>160591</v>
+        <v>178992</v>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Gurgel</t>
+          <t>Vitor Lippi</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS DE AZEVEDO GURGEL</t>
+          <t>VITOR LIPPI</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciusgurgel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G497" s="2" t="inlineStr"/>
-      <c r="H497" s="2" t="inlineStr"/>
+          <t>dep.vitorlippi@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>@vitorlippi</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vitorlippi</t>
+        </is>
+      </c>
       <c r="I497" s="2" t="inlineStr"/>
       <c r="J497" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>178992</v>
+        <v>91228</v>
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>Vitor Lippi</t>
+          <t>Waldemar Oliveira</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>VITOR LIPPI</t>
+          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>dep.vitorlippi@camara.leg.br</t>
+          <t>dep.waldemaroliveira@camara.leg.br</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>@vitorlippi</t>
+          <t>@waldemaroliveiraoficial</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vitorlippi</t>
+          <t>https://instagram.com/waldemaroliveiraoficial</t>
         </is>
       </c>
       <c r="I498" s="2" t="inlineStr"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>91228</v>
+        <v>160569</v>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>Waldemar Oliveira</t>
+          <t>Waldenor Pereira</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
+          <t>WALDENOR ALVES PEREIRA FILHO</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>dep.waldemaroliveira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G499" s="2" t="inlineStr">
-        <is>
-          <t>@waldemaroliveiraoficial</t>
-        </is>
-      </c>
-      <c r="H499" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/waldemaroliveiraoficial</t>
-        </is>
-      </c>
+          <t>dep.waldenorpereira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr"/>
+      <c r="H499" s="2" t="inlineStr"/>
       <c r="I499" s="2" t="inlineStr"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>160569</v>
+        <v>160518</v>
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>Waldenor Pereira</t>
+          <t>Weliton Prado</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>WALDENOR ALVES PEREIRA FILHO</t>
+          <t>WELITON FERNANDES PRADO</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>dep.waldenorpereira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G500" s="2" t="inlineStr"/>
-      <c r="H500" s="2" t="inlineStr"/>
+          <t>dep.welitonprado@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>@weliton.prado</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/weliton.prado</t>
+        </is>
+      </c>
       <c r="I500" s="2" t="inlineStr"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>160518</v>
+        <v>74043</v>
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>Weliton Prado</t>
+          <t>Wellington Roberto</t>
         </is>
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>WELITON FERNANDES PRADO</t>
+          <t>JOSÉ WELLINGTON ROBERTO</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -22465,120 +22473,120 @@
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>dep.welitonprado@camara.leg.br</t>
+          <t>dep.wellingtonroberto@camara.leg.br</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>@weliton.prado</t>
+          <t>@wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/weliton.prado</t>
+          <t>https://instagram.com/wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="I501" s="2" t="inlineStr"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>74043</v>
+        <v>224333</v>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>Wellington Roberto</t>
+          <t>Welter</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ WELLINGTON ROBERTO</t>
+          <t>ELTON CARLOS WELTER</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>dep.wellingtonroberto@camara.leg.br</t>
+          <t>dep.welter@camara.leg.br</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>@wellingtonroberto.pb</t>
+          <t>@eltonwelter</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/wellingtonroberto.pb</t>
+          <t>https://instagram.com/eltonwelter</t>
         </is>
       </c>
       <c r="I502" s="2" t="inlineStr"/>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>224333</v>
+        <v>74044</v>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Welter</t>
+          <t>Wilson Santiago</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>ELTON CARLOS WELTER</t>
+          <t>JOSÉ WILSON SANTIAGO</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>dep.welter@camara.leg.br</t>
+          <t>dep.wilsonsantiago@camara.leg.br</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
         <is>
-          <t>@eltonwelter</t>
+          <t>@wilsonsantiago</t>
         </is>
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/eltonwelter</t>
+          <t>https://instagram.com/wilsonsantiago</t>
         </is>
       </c>
       <c r="I503" s="2" t="inlineStr"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74044</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -22646,7 +22646,7 @@
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>Yury do Paredão</t>
+          <t>Yury Bruno</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>dep.yurydoparedao@camara.leg.br</t>
+          <t>dep.yurybruno@camara.leg.br</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -19451,8 +19451,16 @@
           <t>dep.ricardobarros@camara.leg.br</t>
         </is>
       </c>
-      <c r="G432" s="2" t="inlineStr"/>
-      <c r="H432" s="2" t="inlineStr"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>@ricardobarros.oficial</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardobarros.oficial</t>
+        </is>
+      </c>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -17294,345 +17294,353 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>160556</v>
+        <v>220706</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Padovani</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>NELSON FERNANDO PADOVANI</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.padovani@camara.leg.br</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@nelsinhopadovani</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/nelsinhopadovani</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr"/>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>180214</v>
+        <v>160556</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>@pastordiniz.ad</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="I384" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>160642</v>
+        <v>180214</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G385" s="2" t="inlineStr"/>
-      <c r="H385" s="2" t="inlineStr"/>
+          <t>dep.pastordiniz@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>@pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>204570</v>
+        <v>160642</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>@deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="H386" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr"/>
+      <c r="H386" s="2" t="inlineStr"/>
       <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>220615</v>
+        <v>204570</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorgil@camara.leg.br</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@deputadogildenemyr</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I387" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr"/>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>204553</v>
+        <v>220615</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>@pastorsargentoisidorio</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="I388" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>74160</v>
+        <v>204553</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G389" s="2" t="inlineStr"/>
-      <c r="H389" s="2" t="inlineStr"/>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>@pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>141518</v>
+        <v>74160</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Paulinho da Força</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PAULO PEREIRA DA SILVA</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.paulinhodaforca@camara.leg.br</t>
+          <t>dep.patrusananias@camara.leg.br</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
@@ -17640,37 +17648,37 @@
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>141516</v>
+        <v>141518</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>Paulo Abi-Ackel</t>
+          <t>Paulinho da Força</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>PAULO ABI-ACKEL</t>
+          <t>PAULO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloabiackel@camara.leg.br</t>
+          <t>dep.paulinhodaforca@camara.leg.br</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr"/>
@@ -17678,213 +17686,213 @@
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>220650</v>
+        <v>141516</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Paulo Alexandre Barbosa</t>
+          <t>Paulo Abi-Ackel</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
+          <t>PAULO ABI-ACKEL</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G392" s="2" t="inlineStr">
-        <is>
-          <t>@pauloalexandrebarbosa</t>
-        </is>
-      </c>
-      <c r="H392" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloalexandrebarbosa</t>
-        </is>
-      </c>
+          <t>dep.pauloabiackel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr"/>
+      <c r="H392" s="2" t="inlineStr"/>
       <c r="I392" s="2" t="inlineStr"/>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>178860</v>
+        <v>220650</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>Paulo Azi</t>
+          <t>Paulo Alexandre Barbosa</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>PAULO VELLOSO DANTAS AZI</t>
+          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloazi@camara.leg.br</t>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
         </is>
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>@PauloAziofcial</t>
+          <t>@pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/PauloAziofcial</t>
+          <t>https://instagram.com/pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>160517</v>
+        <v>178860</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Paulo Folletto</t>
+          <t>Paulo Azi</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FOLLETTO</t>
+          <t>PAULO VELLOSO DANTAS AZI</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofolletto@camara.leg.br</t>
+          <t>dep.pauloazi@camara.leg.br</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>@paulo.folletto</t>
+          <t>@PauloAziofcial</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/paulo.folletto</t>
+          <t>https://instagram.com/PauloAziofcial</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr"/>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>160558</v>
+        <v>160517</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Paulo Freire Costa</t>
+          <t>Paulo Folletto</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FREIRE DA COSTA</t>
+          <t>PAULO ROBERTO FOLLETTO</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofreirecosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G395" s="2" t="inlineStr"/>
-      <c r="H395" s="2" t="inlineStr"/>
+          <t>dep.paulofolletto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>@paulo.folletto</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulo.folletto</t>
+        </is>
+      </c>
       <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>204492</v>
+        <v>160558</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Paulo Guedes</t>
+          <t>Paulo Freire Costa</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>PAULO JOSE CARLOS GUEDES</t>
+          <t>PAULO ROBERTO FREIRE DA COSTA</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloguedes@camara.leg.br</t>
+          <t>dep.paulofreirecosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
@@ -17892,22 +17900,22 @@
       <c r="I396" s="2" t="inlineStr"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>233592</v>
+        <v>204492</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Paulo Lemos</t>
+          <t>Paulo Guedes</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
+          <t>PAULO JOSE CARLOS GUEDES</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -17917,100 +17925,100 @@
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>@paulolemosap</t>
-        </is>
-      </c>
-      <c r="H397" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulolemosap</t>
-        </is>
-      </c>
-      <c r="I397" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
-        </is>
-      </c>
+          <t>dep.pauloguedes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr"/>
+      <c r="H397" s="2" t="inlineStr"/>
+      <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>220685</v>
+        <v>233592</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Paulo Litro</t>
+          <t>Paulo Lemos</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
+          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolitro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G398" s="2" t="inlineStr"/>
-      <c r="H398" s="2" t="inlineStr"/>
-      <c r="I398" s="2" t="inlineStr"/>
+          <t>dep.paulolemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>@paulolemosap</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulolemosap</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
+        </is>
+      </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>74574</v>
+        <v>220685</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Paulo Magalhães</t>
+          <t>Paulo Litro</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
+          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomagalhaes@camara.leg.br</t>
+          <t>dep.paulolitro@camara.leg.br</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr"/>
@@ -18018,37 +18026,37 @@
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>74400</v>
+        <v>74574</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Paulo Pimenta</t>
+          <t>Paulo Magalhães</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO SEVERO PIMENTA</t>
+          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.paulopimenta@camara.leg.br</t>
+          <t>dep.paulomagalhaes@camara.leg.br</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr"/>
@@ -18056,37 +18064,37 @@
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>154700</v>
+        <v>74400</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Paulo Soares</t>
+          <t>Paulo Pimenta</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
+          <t>PAULO ROBERTO SEVERO PIMENTA</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.paulosoares@camara.leg.br</t>
+          <t>dep.paulopimenta@camara.leg.br</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr"/>
@@ -18094,27 +18102,27 @@
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>141488</v>
+        <v>154700</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Paulo Soares</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -18124,267 +18132,267 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>@pauloteixeira13</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloteixeira13</t>
-        </is>
-      </c>
+          <t>dep.paulosoares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>220630</v>
+        <v>141488</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pauloteixeira@camara.leg.br</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pauloteixeira13</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pauloteixeira13</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>220667</v>
+        <v>220630</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>@pedrocampospe</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedrocampospe</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>122974</v>
+        <v>220667</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G405" s="2" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr"/>
+          <t>dep.pedrocampos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>@pedrocampospe</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrocampospe</t>
+        </is>
+      </c>
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>204395</v>
+        <v>122974</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G406" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H406" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr"/>
+      <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="2" t="inlineStr"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>122158</v>
+        <v>204395</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr"/>
-      <c r="H407" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I407" s="2" t="inlineStr"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>160604</v>
+        <v>122158</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedropaulo@camara.leg.br</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr"/>
@@ -18392,37 +18400,37 @@
       <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>204406</v>
+        <v>160604</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr"/>
@@ -18430,206 +18438,206 @@
       <c r="I409" s="2" t="inlineStr"/>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>161440</v>
+        <v>204406</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G410" s="2" t="inlineStr">
-        <is>
-          <t>@deputadopezenti</t>
-        </is>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr"/>
+      <c r="H410" s="2" t="inlineStr"/>
       <c r="I410" s="2" t="inlineStr"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>204524</v>
+        <v>161440</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pezenti@camara.leg.br</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@deputadopezenti</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>73486</v>
+        <v>204524</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>@pompeodemattospdt</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
+          <t>https://instagram.com/pinheirinhomg</t>
         </is>
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/PompeodeMattos</t>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>160601</v>
+        <v>73486</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr"/>
-      <c r="H413" s="2" t="inlineStr"/>
-      <c r="I413" s="2" t="inlineStr"/>
+          <t>dep.pompeodemattos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>@pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PompeodeMattos</t>
+        </is>
+      </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>226075</v>
+        <v>160601</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Priscila Costa</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>PRISCILA BEZERRA DA COSTA</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -18639,449 +18647,449 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.priscilacosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>@priscilacosta</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/priscilacosta</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
       <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>220533</v>
+        <v>226075</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Priscila Costa</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>PRISCILA BEZERRA DA COSTA</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.priscilacosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@priscilacosta</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
-        </is>
-      </c>
+          <t>https://instagram.com/priscilacosta</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr"/>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>204390</v>
+        <v>220533</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>@professoralcidesoficial</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
+          <t>https://instagram.com/reginaldo.veras</t>
         </is>
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+          <t>https://youtube.com/Reginaldoveras12</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>221338</v>
+        <v>204390</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr"/>
-      <c r="H417" s="2" t="inlineStr"/>
-      <c r="I417" s="2" t="inlineStr"/>
+          <t>dep.professoralcides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>@professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+        </is>
+      </c>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>160641</v>
+        <v>221338</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr">
-        <is>
-          <t>@profmarcivania</t>
-        </is>
-      </c>
-      <c r="H418" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr"/>
+      <c r="H418" s="2" t="inlineStr"/>
       <c r="I418" s="2" t="inlineStr"/>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>220586</v>
+        <v>160641</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
+          <t>dep.professoramarcivania@camara.leg.br</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>@rafaelbrito15</t>
+          <t>@profmarcivania</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr"/>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>233594</v>
+        <v>220586</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G420" s="2" t="inlineStr"/>
-      <c r="H420" s="2" t="inlineStr"/>
-      <c r="I420" s="2" t="inlineStr"/>
+          <t>dep.rafaelbrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>220532</v>
+        <v>233594</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="H421" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I421" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr"/>
+      <c r="H421" s="2" t="inlineStr"/>
+      <c r="I421" s="2" t="inlineStr"/>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>220626</v>
+        <v>220532</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
+          <t>dep.rafaelprudente@camara.leg.br</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>@rafaelsimoesmg</t>
+          <t>@rafaelprudentedep</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="I422" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>204567</v>
+        <v>220626</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr"/>
-      <c r="H423" s="2" t="inlineStr"/>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>74084</v>
+        <v>204567</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -19091,89 +19099,85 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H424" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I424" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr"/>
+      <c r="H424" s="2" t="inlineStr"/>
+      <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>74161</v>
+        <v>74084</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G425" s="2" t="inlineStr"/>
-      <c r="H425" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>220606</v>
+        <v>74161</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -19183,620 +19187,624 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="2" t="inlineStr"/>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>153423</v>
+        <v>220606</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G427" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H427" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.reimont@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr"/>
+      <c r="H427" s="2" t="inlineStr"/>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>73801</v>
+        <v>153423</v>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr"/>
-      <c r="H428" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I428" s="2" t="inlineStr"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>175765</v>
+        <v>73801</v>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>@ribamarsilvaoficial</t>
-        </is>
-      </c>
-      <c r="H429" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr"/>
       <c r="I429" s="2" t="inlineStr"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>221329</v>
+        <v>175765</v>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Abrão</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MARTINS DAVID</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoabrao@camara.leg.br</t>
+          <t>dep.ribamarsilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>@ricardoabraooficial</t>
+          <t>@ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoabraooficial</t>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr"/>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>220543</v>
+        <v>221329</v>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Ayres</t>
+          <t>Ricardo Abrão</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>RICARDO AYRES DE CARVALHO</t>
+          <t>RICARDO MARTINS DAVID</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoayres@camara.leg.br</t>
+          <t>dep.ricardoabrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>@ricardoayres_to</t>
+          <t>@ricardoabraooficial</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoayres_to</t>
+          <t>https://instagram.com/ricardoabraooficial</t>
         </is>
       </c>
       <c r="I431" s="2" t="inlineStr"/>
       <c r="J431" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>73788</v>
+        <v>220543</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Barros</t>
+          <t>Ricardo Ayres</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
+          <t>RICARDO AYRES DE CARVALHO</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardobarros@camara.leg.br</t>
+          <t>dep.ricardoayres@camara.leg.br</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>@ricardobarros.oficial</t>
+          <t>@ricardoayres_to</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardobarros.oficial</t>
+          <t>https://instagram.com/ricardoayres_to</t>
         </is>
       </c>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>204362</v>
+        <v>73788</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Guidi</t>
+          <t>Ricardo Barros</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>RICARDO ZANATTA GUIDI</t>
+          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoguidi@camara.leg.br</t>
+          <t>dep.ricardobarros@camara.leg.br</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>@ricardozguidi</t>
+          <t>@ricardobarros.oficial</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardozguidi</t>
+          <t>https://instagram.com/ricardobarros.oficial</t>
         </is>
       </c>
       <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>220694</v>
+        <v>204362</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Maia</t>
+          <t>Ricardo Guidi</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MAIA CHAVES DE SOUZA</t>
+          <t>RICARDO ZANATTA GUIDI</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardomaia@camara.leg.br</t>
+          <t>dep.ricardoguidi@camara.leg.br</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>@ricardomaia.dabahia</t>
+          <t>@ricardozguidi</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="I434" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/ricardomaiadabahia5610</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ricardozguidi</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr"/>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>220633</v>
+        <v>220694</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Salles</t>
+          <t>Ricardo Maia</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DE AQUINO SALLES</t>
+          <t>RICARDO MAIA CHAVES DE SOUZA</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardosalles@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G435" s="2" t="inlineStr"/>
-      <c r="H435" s="2" t="inlineStr"/>
-      <c r="I435" s="2" t="inlineStr"/>
+          <t>dep.ricardomaia@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>@ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/ricardomaiadabahia5610</t>
+        </is>
+      </c>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>204489</v>
+        <v>220633</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Robério Monteiro</t>
+          <t>Ricardo Salles</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
+          <t>RICARDO DE AQUINO SALLES</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>dep.roberiomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>@dep.roberiomonteiro</t>
-        </is>
-      </c>
-      <c r="H436" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.roberiomonteiro</t>
-        </is>
-      </c>
+          <t>dep.ricardosalles@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr"/>
+      <c r="H436" s="2" t="inlineStr"/>
       <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>220693</v>
+        <v>204489</v>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Roberta Roma</t>
+          <t>Robério Monteiro</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Roberta de Araujo Costa Roma</t>
+          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>dep.robertaroma@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr"/>
-      <c r="H437" s="2" t="inlineStr"/>
+          <t>dep.roberiomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>@dep.roberiomonteiro</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.roberiomonteiro</t>
+        </is>
+      </c>
       <c r="I437" s="2" t="inlineStr"/>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>220588</v>
+        <v>220693</v>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Roberto Duarte</t>
+          <t>Roberta Roma</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO DUARTE JUNIOR</t>
+          <t>Roberta de Araujo Costa Roma</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>dep.robertoduarte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>@rdnarede</t>
-        </is>
-      </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rdnarede</t>
-        </is>
-      </c>
+          <t>dep.robertaroma@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
+      <c r="H438" s="2" t="inlineStr"/>
       <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>220613</v>
+        <v>220588</v>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Roberto Monteiro Pai</t>
+          <t>Roberto Duarte</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
+          <t>ROBERTO DUARTE JUNIOR</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>dep.robertomonteiropai@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr"/>
-      <c r="H439" s="2" t="inlineStr"/>
+          <t>dep.robertoduarte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>@rdnarede</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rdnarede</t>
+        </is>
+      </c>
       <c r="I439" s="2" t="inlineStr"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>220624</v>
+        <v>220613</v>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Robinson Faria</t>
+          <t>Roberto Monteiro Pai</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>ROBINSON MESQUITA DE FARIA</t>
+          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>dep.robinsonfaria@camara.leg.br</t>
+          <t>dep.robertomonteiropai@camara.leg.br</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
@@ -19804,72 +19812,60 @@
       <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>220546</v>
+        <v>220624</v>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Rodolfo Nogueira</t>
+          <t>Robinson Faria</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
+          <t>ROBINSON MESQUITA DE FARIA</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>dep.rodolfonogueira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>@rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="I441" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RodolfoNogueirams</t>
-        </is>
-      </c>
+          <t>dep.robinsonfaria@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr"/>
+      <c r="H441" s="2" t="inlineStr"/>
+      <c r="I441" s="2" t="inlineStr"/>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>230767</v>
+        <v>220546</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo da Zaeli</t>
+          <t>Rodolfo Nogueira</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO LUGLI</t>
+          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -19879,445 +19875,457 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodazaeli@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G442" s="2" t="inlineStr"/>
-      <c r="H442" s="2" t="inlineStr"/>
-      <c r="I442" s="2" t="inlineStr"/>
+          <t>dep.rodolfonogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>@rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RodolfoNogueirams</t>
+        </is>
+      </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>141531</v>
+        <v>230767</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo de Castro</t>
+          <t>Rodrigo da Zaeli</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO BATISTA DE CASTRO</t>
+          <t>RODRIGO LUGLI</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodecastro@camara.leg.br</t>
+          <t>dep.rodrigodazaeli@camara.leg.br</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr"/>
-      <c r="I443" s="2" t="inlineStr">
-        <is>
-          <t>http://www.youtube.com/rodrigocastro45</t>
-        </is>
-      </c>
+      <c r="I443" s="2" t="inlineStr"/>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>220641</v>
+        <v>141531</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Gambale</t>
+          <t>Rodrigo de Castro</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO GAMBALE VIEIRA</t>
+          <t>RODRIGO BATISTA DE CASTRO</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigogambale@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigogambale</t>
-        </is>
-      </c>
-      <c r="H444" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigogambale</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr"/>
+          <t>dep.rodrigodecastro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr"/>
+      <c r="H444" s="2" t="inlineStr"/>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/rodrigocastro45</t>
+        </is>
+      </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>141533</v>
+        <v>220641</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Rollemberg</t>
+          <t>Rodrigo Gambale</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SOBRAL ROLLEMBERG</t>
+          <t>RODRIGO GAMBALE VIEIRA</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigorollemberg@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G445" s="2" t="inlineStr"/>
-      <c r="H445" s="2" t="inlineStr"/>
+          <t>dep.rodrigogambale@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigogambale</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigogambale</t>
+        </is>
+      </c>
       <c r="I445" s="2" t="inlineStr"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>165470</v>
+        <v>141533</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Valadares</t>
+          <t>Rodrigo Rollemberg</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SANTANA VALADARES</t>
+          <t>RODRIGO SOBRAL ROLLEMBERG</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigovaladares@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="H446" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadorodrigovaladares1954</t>
-        </is>
-      </c>
+          <t>dep.rodrigorollemberg@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr"/>
+      <c r="H446" s="2" t="inlineStr"/>
+      <c r="I446" s="2" t="inlineStr"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>220695</v>
+        <v>165470</v>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Rogéria Santos</t>
+          <t>Rodrigo Valadares</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
+          <t>RODRIGO SANTANA VALADARES</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriasantos@camara.leg.br</t>
+          <t>dep.rodrigovaladares@camara.leg.br</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>@rogeriasantosoficial</t>
+          <t>@rodrigovaladares_</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriasantosoficial</t>
+          <t>https://instagram.com/rodrigovaladares_</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
+          <t>https://youtube.com/deputadorodrigovaladares1954</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>204480</v>
+        <v>220695</v>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Rogério Correia</t>
+          <t>Rogéria Santos</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
+          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriocorreia@camara.leg.br</t>
+          <t>dep.rogeriasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>@rogeriocorreia_</t>
+          <t>@rogeriasantosoficial</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriocorreia_</t>
+          <t>https://instagram.com/rogeriasantosoficial</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
+          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>204525</v>
+        <v>204480</v>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Rosana Valle</t>
+          <t>Rogério Correia</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>ROSANA DE OLIVEIRA VALLE</t>
+          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>dep.rosanavalle@camara.leg.br</t>
+          <t>dep.rogeriocorreia@camara.leg.br</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>@rosanavalleoficial</t>
+          <t>@rogeriocorreia_</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosanavalleoficial</t>
+          <t>https://instagram.com/rogeriocorreia_</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>178945</v>
+        <v>204525</v>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Gomes</t>
+          <t>Rosana Valle</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE SOUZA GOMES</t>
+          <t>ROSANA DE OLIVEIRA VALLE</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelagomes@camara.leg.br</t>
+          <t>dep.rosanavalle@camara.leg.br</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>@rosangelasgomes</t>
+          <t>@rosanavalleoficial</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosangelasgomes</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rosanavalleoficial</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+        </is>
+      </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>220644</v>
+        <v>178945</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Moro</t>
+          <t>Rosangela Gomes</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
+          <t>ROSANGELA DE SOUZA GOMES</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelamoro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr"/>
-      <c r="H451" s="2" t="inlineStr"/>
+          <t>dep.rosangelagomes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelasgomes</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelasgomes</t>
+        </is>
+      </c>
       <c r="I451" s="2" t="inlineStr"/>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>220620</v>
+        <v>220644</v>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Rosângela Reis</t>
+          <t>Rosangela Moro</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
+          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -20327,81 +20335,81 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelareis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelareis.mg</t>
-        </is>
-      </c>
-      <c r="H452" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelareis.mg</t>
-        </is>
-      </c>
+          <t>dep.rosangelamoro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr"/>
+      <c r="H452" s="2" t="inlineStr"/>
       <c r="I452" s="2" t="inlineStr"/>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>74371</v>
+        <v>220620</v>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Rubens Otoni</t>
+          <t>Rosângela Reis</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>RUBENS OTONI GOMIDE</t>
+          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>dep.rubensotoni@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G453" s="2" t="inlineStr"/>
-      <c r="H453" s="2" t="inlineStr"/>
+          <t>dep.rosangelareis@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelareis.mg</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelareis.mg</t>
+        </is>
+      </c>
       <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>178887</v>
+        <v>74371</v>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Rubens Pereira Júnior</t>
+          <t>Rubens Otoni</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
+          <t>RUBENS OTONI GOMIDE</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -20411,47 +20419,35 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>dep.rubenspereirajunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>@rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="H454" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
-        </is>
-      </c>
+          <t>dep.rubensotoni@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr"/>
+      <c r="H454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr"/>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>73604</v>
+        <v>178887</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Rui Falcão</t>
+          <t>Rubens Pereira Júnior</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>RUI GOETHE DA COSTA FALCÃO</t>
+          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -20461,286 +20457,298 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>dep.ruifalcao@camara.leg.br</t>
+          <t>dep.rubenspereirajunior@camara.leg.br</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>@ruifalcao13</t>
+          <t>@rubenspereirajr</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruifalcao13</t>
+          <t>https://instagram.com/rubenspereirajr</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/rfalcao13</t>
+          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>160635</v>
+        <v>73604</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Ruy Carneiro</t>
+          <t>Rui Falcão</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
+          <t>RUI GOETHE DA COSTA FALCÃO</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>dep.ruycarneiro@camara.leg.br</t>
+          <t>dep.ruifalcao@camara.leg.br</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>@ruy.carneiro</t>
+          <t>@ruifalcao13</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruy.carneiro</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr"/>
+          <t>https://instagram.com/ruifalcao13</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/rfalcao13</t>
+        </is>
+      </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>204535</v>
+        <v>160635</v>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Sâmia Bomfim</t>
+          <t>Ruy Carneiro</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>SAMIA DE SOUZA BOMFIM</t>
+          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>dep.samiabomfim@camara.leg.br</t>
+          <t>dep.ruycarneiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>@samiabomfim</t>
+          <t>@ruy.carneiro</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/samiabomfim</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/samiabomfimpsol</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ruy.carneiro</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr"/>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>220631</v>
+        <v>204535</v>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Samuel Viana</t>
+          <t>Sâmia Bomfim</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
+          <t>SAMIA DE SOUZA BOMFIM</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>dep.samuelviana@camara.leg.br</t>
+          <t>dep.samiabomfim@camara.leg.br</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>@vianasamuel</t>
+          <t>@samiabomfim</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vianasamuel</t>
+          <t>https://instagram.com/samiabomfim</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
+          <t>https://youtube.com/samiabomfimpsol</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>204416</v>
+        <v>220631</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Samuel Viana</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>UBIRATAN ANTUNES SANDERSON</t>
+          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>dep.sanderson@camara.leg.br</t>
+          <t>dep.samuelviana@camara.leg.br</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>@sandersonrs</t>
+          <t>@vianasamuel</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sandersonrs</t>
+          <t>https://instagram.com/vianasamuel</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>160621</v>
+        <v>204416</v>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Sandro Alex</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
+          <t>UBIRATAN ANTUNES SANDERSON</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>dep.sandroalex@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
-      <c r="I460" s="2" t="inlineStr"/>
+          <t>dep.sanderson@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>@sandersonrs</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sandersonrs</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+        </is>
+      </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>236518</v>
+        <v>160621</v>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Santin Roveda</t>
+          <t>Sandro Alex</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>HILTON SANTIN ROVEDA</t>
+          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -20750,23 +20758,15 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>dep.santinroveda@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>@santinroveda</t>
-        </is>
-      </c>
-      <c r="H461" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/santinroveda</t>
-        </is>
-      </c>
+          <t>dep.sandroalex@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr"/>
+      <c r="H461" s="2" t="inlineStr"/>
       <c r="I461" s="2" t="inlineStr"/>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -17060,572 +17060,564 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>194260</v>
+        <v>204498</v>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Nivaldo Albuquerque</t>
+          <t>Olival Marques</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>NIVALDO FERREIRA DE ALBUQUERQUE NETO</t>
+          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>dep.nivaldoalbuquerque@camara.leg.br</t>
+          <t>dep.olivalmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>@nivaldoalbuquerque</t>
+          <t>@OlivalMarques</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nivaldoalbuquerque</t>
+          <t>https://instagram.com/OlivalMarques</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/194260</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>204498</v>
+        <v>178987</v>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Olival Marques</t>
+          <t>Orlando Silva</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
+          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>dep.olivalmarques@camara.leg.br</t>
+          <t>dep.orlandosilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>@OlivalMarques</t>
+          <t>@orlandosilvasp</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/OlivalMarques</t>
+          <t>https://instagram.com/orlandosilvasp</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr"/>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>178987</v>
+        <v>73692</v>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Orlando Silva</t>
+          <t>Osmar Terra</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
+          <t>OSMAR GASPARINI TERRA</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>dep.orlandosilva@camara.leg.br</t>
+          <t>dep.osmarterra@camara.leg.br</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>@orlandosilvasp</t>
+          <t>@terra.osmar</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/orlandosilvasp</t>
-        </is>
-      </c>
-      <c r="I380" s="2" t="inlineStr"/>
+          <t>https://instagram.com/terra.osmar</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
+        </is>
+      </c>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>73692</v>
+        <v>204441</v>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Osmar Terra</t>
+          <t>Otoni de Paula</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>OSMAR GASPARINI TERRA</t>
+          <t>OTONI MOURA DE PAULO JUNIOR</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>dep.osmarterra@camara.leg.br</t>
+          <t>dep.otonidepaula@camara.leg.br</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>@terra.osmar</t>
+          <t>@otonidepaulaoficial</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/terra.osmar</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/otonidepaulaoficial</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr"/>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>204441</v>
+        <v>220706</v>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Otoni de Paula</t>
+          <t>Padovani</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>OTONI MOURA DE PAULO JUNIOR</t>
+          <t>NELSON FERNANDO PADOVANI</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>dep.otonidepaula@camara.leg.br</t>
+          <t>dep.padovani@camara.leg.br</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>@otonidepaulaoficial</t>
+          <t>@nelsinhopadovani</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/otonidepaulaoficial</t>
+          <t>https://instagram.com/nelsinhopadovani</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr"/>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>220706</v>
+        <v>160556</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Padovani</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>NELSON FERNANDO PADOVANI</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.padovani@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>@nelsinhopadovani</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsinhopadovani</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>160556</v>
+        <v>180214</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.pastordiniz@camara.leg.br</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@pastordiniz.ad</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I384" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr"/>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>180214</v>
+        <v>160642</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G385" s="2" t="inlineStr">
-        <is>
-          <t>@pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr"/>
+      <c r="H385" s="2" t="inlineStr"/>
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>160642</v>
+        <v>204570</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G386" s="2" t="inlineStr"/>
-      <c r="H386" s="2" t="inlineStr"/>
+          <t>dep.pastorgil@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>@deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
       <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>204570</v>
+        <v>220615</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>@deputadogildenemyr</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="I387" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>220615</v>
+        <v>204553</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@pastorsargentoisidorio</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I388" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>204553</v>
+        <v>74160</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>@pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="H389" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
+          <t>dep.patrusananias@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr"/>
+      <c r="H389" s="2" t="inlineStr"/>
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>74160</v>
+        <v>171617</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Paulão</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>PAULO FERNANDO DOS SANTOS</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -17635,12 +17627,12 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
+          <t>dep.paulao@camara.leg.br</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr"/>
@@ -17648,7 +17640,7 @@
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -11698,16 +11698,16 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>141459</v>
+        <v>74550</v>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>João Maia</t>
+          <t>João Leão</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>JOÃO DA SILVA MAIA</t>
+          <t>JOÃO FELIPE DE SOUZA LEÃO</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>dep.joaomaia@camara.leg.br</t>
+          <t>dep.joaoleao@camara.leg.br</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr"/>
@@ -11730,137 +11730,137 @@
       <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141459</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74550</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>178910</v>
+        <v>141459</v>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Passarinho</t>
+          <t>João Maia</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>JOAQUIM PASSARINHO PINTO DE SOUZA PORTO</t>
+          <t>JOÃO DA SILVA MAIA</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>dep.joaquimpassarinho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>@joaquim_passarinho</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/joaquim_passarinho</t>
-        </is>
-      </c>
+          <t>dep.joaomaia@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="2" t="inlineStr"/>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178910</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141459</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>160548</v>
+        <v>178910</v>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Jonas Donizette</t>
+          <t>Joaquim Passarinho</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>JONAS DONIZETTE FERREIRA</t>
+          <t>JOAQUIM PASSARINHO PINTO DE SOUZA PORTO</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>dep.jonasdonizette@camara.leg.br</t>
+          <t>dep.joaquimpassarinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>@jonasdonizette</t>
+          <t>@joaquim_passarinho</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/jonasdonizette</t>
+          <t>https://instagram.com/joaquim_passarinho</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160548</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178910</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>235800</v>
+        <v>160548</v>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Jorge Araújo</t>
+          <t>Jonas Donizette</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>JORGE SILVA DE ARAÚJO</t>
+          <t>JONAS DONIZETTE FERREIRA</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>dep.jorgearaujo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr"/>
+          <t>dep.jonasdonizette@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>@jonasdonizette</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jonasdonizette</t>
+        </is>
+      </c>
       <c r="I260" s="2" t="inlineStr"/>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235800</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160548</t>
         </is>
       </c>
     </row>
@@ -13818,154 +13818,162 @@
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
-        <v>178954</v>
+        <v>220616</v>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Lucio Mosquini</t>
+          <t>Luciano Vieira</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>LUCIO ANTONIO MOSQUINI</t>
+          <t>LUCIANO VIEIRA MENDES</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>dep.luciomosquini@camara.leg.br</t>
+          <t>dep.lucianovieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>@luciomosquini</t>
+          <t>@lucianovieirarj</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/luciomosquini</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/lucioantoniomosquinimosqui7885</t>
-        </is>
-      </c>
+          <t>https://instagram.com/lucianovieirarj</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr"/>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178954</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220616</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
-        <v>160510</v>
+        <v>178954</v>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Luis Tibé</t>
+          <t>Lucio Mosquini</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>LUIS HENRIQUE DE OLIVEIRA RESENDE</t>
+          <t>LUCIO ANTONIO MOSQUINI</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>dep.luistibe@camara.leg.br</t>
+          <t>dep.luciomosquini@camara.leg.br</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>@deputadoluistibe</t>
+          <t>@luciomosquini</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadoluistibe</t>
+          <t>https://instagram.com/luciomosquini</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BuVmJsuVjuY</t>
+          <t>https://youtube.com/lucioantoniomosquinimosqui7885</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160510</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178954</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>204410</v>
+        <v>160510</v>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Luisa Canziani</t>
+          <t>Luis Tibé</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>LUISA CANZIANI DOS SANTOS SILVEIRA</t>
+          <t>LUIS HENRIQUE DE OLIVEIRA RESENDE</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>dep.luisacanziani@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G307" s="2" t="inlineStr"/>
-      <c r="H307" s="2" t="inlineStr"/>
-      <c r="I307" s="2" t="inlineStr"/>
+          <t>dep.luistibe@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>@deputadoluistibe</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadoluistibe</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BuVmJsuVjuY</t>
+        </is>
+      </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204410</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160510</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>141485</v>
+        <v>204410</v>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Busato</t>
+          <t>Luisa Canziani</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS GHIORZZI BUSATO</t>
+          <t>LUISA CANZIANI DOS SANTOS SILVEIRA</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -13975,196 +13983,196 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarlosbusato@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>@lcbusato</t>
-        </is>
-      </c>
-      <c r="H308" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/lcbusato</t>
-        </is>
-      </c>
-      <c r="I308" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCI1WRKDHZA-6HQwN5_yWypw</t>
-        </is>
-      </c>
+          <t>dep.luisacanziani@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr"/>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141485</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204410</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
-        <v>73778</v>
+        <v>141485</v>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Hauly</t>
+          <t>Luiz Carlos Busato</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS JORGE HAULY</t>
+          <t>LUIZ CARLOS GHIORZZI BUSATO</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarloshauly@camara.leg.br</t>
+          <t>dep.luizcarlosbusato@camara.leg.br</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>@deputadohauly</t>
+          <t>@lcbusato</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadohauly</t>
-        </is>
-      </c>
-      <c r="I309" s="2" t="inlineStr"/>
+          <t>https://instagram.com/lcbusato</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCI1WRKDHZA-6HQwN5_yWypw</t>
+        </is>
+      </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73778</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141485</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>204485</v>
+        <v>73778</v>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Motta</t>
+          <t>Luiz Carlos Hauly</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS MOTTA</t>
+          <t>LUIZ CARLOS JORGE HAULY</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarlosmotta@camara.leg.br</t>
+          <t>dep.luizcarloshauly@camara.leg.br</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>@deputadomotta</t>
+          <t>@deputadohauly</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadomotta</t>
-        </is>
-      </c>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@DeputadoMotta</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadohauly</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204485</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73778</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
-        <v>74041</v>
+        <v>204485</v>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Luiz Couto</t>
+          <t>Luiz Carlos Motta</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>LUIZ ALBUQUERQUE COUTO</t>
+          <t>LUIZ CARLOS MOTTA</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcouto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr"/>
-      <c r="H311" s="2" t="inlineStr"/>
-      <c r="I311" s="2" t="inlineStr"/>
+          <t>dep.luizcarlosmotta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>@deputadomotta</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadomotta</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DeputadoMotta</t>
+        </is>
+      </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74041</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204485</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
-        <v>141487</v>
+        <v>74041</v>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Luiz Fernando Faria</t>
+          <t>Luiz Couto</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>LUIZ FERNANDO RAMOS FARIA</t>
+          <t>LUIZ ALBUQUERQUE COUTO</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>dep.luizfernandofaria@camara.leg.br</t>
+          <t>dep.luizcouto@camara.leg.br</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr"/>
@@ -14172,37 +14180,37 @@
       <c r="I312" s="2" t="inlineStr"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141487</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74041</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
-        <v>220658</v>
+        <v>141487</v>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Luiz Gastão</t>
+          <t>Luiz Fernando Faria</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>LUIZ GASTÃO BITTENCOURT DA SILVA</t>
+          <t>LUIZ FERNANDO RAMOS FARIA</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>dep.luizgastao@camara.leg.br</t>
+          <t>dep.luizfernandofaria@camara.leg.br</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr"/>
@@ -14210,165 +14218,153 @@
       <c r="I313" s="2" t="inlineStr"/>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220658</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141487</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
-        <v>204455</v>
+        <v>220658</v>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Luiz Lima</t>
+          <t>Luiz Gastão</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>LUIZ EDUARDO CARNEIRO DA SILVA DE SOUZA LIMA</t>
+          <t>LUIZ GASTÃO BITTENCOURT DA SILVA</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>dep.luizlima@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>@oficialluizlima</t>
-        </is>
-      </c>
-      <c r="H314" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/oficialluizlima</t>
-        </is>
-      </c>
-      <c r="I314" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/oficialluizlima</t>
-        </is>
-      </c>
+          <t>dep.luizgastao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr"/>
+      <c r="H314" s="2" t="inlineStr"/>
+      <c r="I314" s="2" t="inlineStr"/>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204455</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220658</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
-        <v>162332</v>
+        <v>204455</v>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Luiz Nishimori</t>
+          <t>Luiz Lima</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>LUIZ HILOSHI NISHIMORI</t>
+          <t>LUIZ EDUARDO CARNEIRO DA SILVA DE SOUZA LIMA</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>dep.luiznishimori@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G315" s="2" t="inlineStr"/>
-      <c r="H315" s="2" t="inlineStr"/>
-      <c r="I315" s="2" t="inlineStr"/>
+          <t>dep.luizlima@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>@oficialluizlima</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oficialluizlima</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/oficialluizlima</t>
+        </is>
+      </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162332</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204455</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
-        <v>204526</v>
+        <v>162332</v>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Luiz Philippe de Orleans e Bragança</t>
+          <t>Luiz Nishimori</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PHILIPPE DE ORLEANS BRAGANÇA</t>
+          <t>LUIZ HILOSHI NISHIMORI</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>dep.luizphilippedeorleansebraganca@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G316" s="2" t="inlineStr">
-        <is>
-          <t>@lpbragancabr</t>
-        </is>
-      </c>
-      <c r="H316" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/lpbragancabr</t>
-        </is>
-      </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/luizphilippebr</t>
-        </is>
-      </c>
+          <t>dep.luiznishimori@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr"/>
+      <c r="H316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204526</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162332</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
-        <v>74784</v>
+        <v>204526</v>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Luiza Erundina</t>
+          <t>Luiz Philippe de Orleans e Bragança</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>LUIZA ERUNDINA DE SOUSA</t>
+          <t>LUIZ PHILIPPE DE ORLEANS BRAGANÇA</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -14378,45 +14374,57 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>dep.luizaerundina@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G317" s="2" t="inlineStr"/>
-      <c r="H317" s="2" t="inlineStr"/>
-      <c r="I317" s="2" t="inlineStr"/>
+          <t>dep.luizphilippedeorleansebraganca@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>@lpbragancabr</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lpbragancabr</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/luizphilippebr</t>
+        </is>
+      </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74784</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204526</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
-        <v>178866</v>
+        <v>74784</v>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Luizianne Lins</t>
+          <t>Luiza Erundina</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>LUIZIANNE DE OLIVEIRA LINS</t>
+          <t>LUIZA ERUNDINA DE SOUSA</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>REDE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>dep.luiziannelins@camara.leg.br</t>
+          <t>dep.luizaerundina@camara.leg.br</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr"/>
@@ -14424,37 +14432,37 @@
       <c r="I318" s="2" t="inlineStr"/>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178866</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74784</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
-        <v>220669</v>
+        <v>178866</v>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Lula da Fonte</t>
+          <t>Luizianne Lins</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>LUIZ EDUARDO DE QUEIROZ CAMPOS DA FONTE ALBUQUERQUE</t>
+          <t>LUIZIANNE DE OLIVEIRA LINS</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REDE</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>dep.luladafonte@camara.leg.br</t>
+          <t>dep.luiziannelins@camara.leg.br</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr"/>
@@ -14462,267 +14470,267 @@
       <c r="I319" s="2" t="inlineStr"/>
       <c r="J319" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220669</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178866</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
-        <v>166402</v>
+        <v>220669</v>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Magda Mofatto</t>
+          <t>Lula da Fonte</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>MAGDA MOFATTO HON</t>
+          <t>LUIZ EDUARDO DE QUEIROZ CAMPOS DA FONTE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>dep.magdamofatto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>@magdamofatto.goias</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/magdamofatto.goias</t>
-        </is>
-      </c>
+          <t>dep.luladafonte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr"/>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/166402</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220669</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
-        <v>220648</v>
+        <v>166402</v>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Marangoni</t>
+          <t>Magda Mofatto</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO JOSE DE SOUZA MARANGONI</t>
+          <t>MAGDA MOFATTO HON</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>dep.marangoni@camara.leg.br</t>
+          <t>dep.magdamofatto@camara.leg.br</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>@marangoni.oficial</t>
+          <t>@magdamofatto.goias</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marangoni.oficial</t>
-        </is>
-      </c>
-      <c r="I321" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@fernandomarangoni99/</t>
-        </is>
-      </c>
+          <t>https://instagram.com/magdamofatto.goias</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr"/>
       <c r="J321" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220648</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/166402</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>156190</v>
+        <v>220648</v>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Marcel van Hattem</t>
+          <t>Marangoni</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>MARCEL VAN HATTEM</t>
+          <t>FERNANDO JOSE DE SOUZA MARANGONI</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelvanhattem@camara.leg.br</t>
+          <t>dep.marangoni@camara.leg.br</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>@MARCELVANHATTEM</t>
+          <t>@marangoni.oficial</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/MARCELVANHATTEM</t>
+          <t>https://instagram.com/marangoni.oficial</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCAGHY76tgzPiiXpJtM1sVCg</t>
+          <t>https://www.youtube.com/@fernandomarangoni99/</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/156190</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220648</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>179000</v>
+        <v>156190</v>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Álvaro Antônio</t>
+          <t>Marcel van Hattem</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>MARCELO HENRIQUE TEIXEIRA DIAS</t>
+          <t>MARCEL VAN HATTEM</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>dep.marceloalvaroantonio@camara.leg.br</t>
+          <t>dep.marcelvanhattem@camara.leg.br</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>@marceloalvaroantonio</t>
+          <t>@MARCELVANHATTEM</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marceloalvaroantonio</t>
-        </is>
-      </c>
-      <c r="I323" s="2" t="inlineStr"/>
+          <t>https://instagram.com/MARCELVANHATTEM</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCAGHY76tgzPiiXpJtM1sVCg</t>
+        </is>
+      </c>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179000</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/156190</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>220599</v>
+        <v>179000</v>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Crivella</t>
+          <t>Marcelo Álvaro Antônio</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>MARCELO BEZERRA  CRIVELLA</t>
+          <t>MARCELO HENRIQUE TEIXEIRA DIAS</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelocrivella@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G324" s="2" t="inlineStr"/>
-      <c r="H324" s="2" t="inlineStr"/>
+          <t>dep.marceloalvaroantonio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>@marceloalvaroantonio</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/marceloalvaroantonio</t>
+        </is>
+      </c>
       <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220599</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179000</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>133810</v>
+        <v>220599</v>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Moraes</t>
+          <t>Marcelo Crivella</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>MARCELO PIRES MORAES</t>
+          <t>MARCELO BEZERRA  CRIVELLA</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelomoraes@camara.leg.br</t>
+          <t>dep.marcelocrivella@camara.leg.br</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr"/>
@@ -14730,37 +14738,37 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/133810</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220599</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>204558</v>
+        <v>133810</v>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Nilo</t>
+          <t>Marcelo Moraes</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ MARCELO DO NASCIMENTO NILO</t>
+          <t>MARCELO PIRES MORAES</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelonilo@camara.leg.br</t>
+          <t>dep.marcelomoraes@camara.leg.br</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr"/>
@@ -14768,37 +14776,37 @@
       <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/133810</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>160161</v>
+        <v>204558</v>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Queiroz</t>
+          <t>Marcelo Nilo</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>MARCELO ANDRE CID HERACLITO DO PORTO QUEIROZ</t>
+          <t>JOSÉ MARCELO DO NASCIMENTO NILO</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>dep.marceloqueiroz@camara.leg.br</t>
+          <t>dep.marcelonilo@camara.leg.br</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr"/>
@@ -14806,37 +14814,37 @@
       <c r="I327" s="2" t="inlineStr"/>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204558</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>178983</v>
+        <v>160161</v>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Marcio Alvino</t>
+          <t>Marcelo Queiroz</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>MARCIO LUIZ ALVINO DE SOUZA</t>
+          <t>MARCELO ANDRE CID HERACLITO DO PORTO QUEIROZ</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>dep.marcioalvino@camara.leg.br</t>
+          <t>dep.marceloqueiroz@camara.leg.br</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr"/>
@@ -14844,37 +14852,37 @@
       <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178983</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160161</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>179001</v>
+        <v>178983</v>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Márcio Biolchi</t>
+          <t>Marcio Alvino</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>MARCIO DELLA VALLE BIOLCHI</t>
+          <t>MARCIO LUIZ ALVINO DE SOUZA</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>dep.marciobiolchi@camara.leg.br</t>
+          <t>dep.marcioalvino@camara.leg.br</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr"/>
@@ -14882,73 +14890,65 @@
       <c r="I329" s="2" t="inlineStr"/>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179001</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178983</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>220687</v>
+        <v>179001</v>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Márcio Honaiser</t>
+          <t>Márcio Biolchi</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>MARCIO JOSE HONAISER</t>
+          <t>MARCIO DELLA VALLE BIOLCHI</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>dep.marciohonaiser@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G330" s="2" t="inlineStr">
-        <is>
-          <t>@marciohonaiser</t>
-        </is>
-      </c>
-      <c r="H330" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/marciohonaiser</t>
-        </is>
-      </c>
+          <t>dep.marciobiolchi@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr"/>
+      <c r="H330" s="2" t="inlineStr"/>
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220687</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179001</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>81055</v>
+        <v>220687</v>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Márcio Jerry</t>
+          <t>Márcio Honaiser</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>MÁRCIO JERRY SARAIVA BARROSO</t>
+          <t>MARCIO JOSE HONAISER</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -14958,207 +14958,207 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>dep.marciojerry@camara.leg.br</t>
+          <t>dep.marciohonaiser@camara.leg.br</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>@marciojerry</t>
+          <t>@marciohonaiser</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marciojerry</t>
-        </is>
-      </c>
-      <c r="I331" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/marciojerry</t>
-        </is>
-      </c>
+          <t>https://instagram.com/marciohonaiser</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/81055</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220687</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
-        <v>150418</v>
+        <v>81055</v>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Márcio Marinho</t>
+          <t>Márcio Jerry</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>MÁRCIO CARLOS MARINHO</t>
+          <t>MÁRCIO JERRY SARAIVA BARROSO</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>dep.marciomarinho@camara.leg.br</t>
+          <t>dep.marciojerry@camara.leg.br</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>@deputadomarciomarinho</t>
+          <t>@marciojerry</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadomarciomarinho</t>
+          <t>https://instagram.com/marciojerry</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCx3t_YQx8H-93UD5k9Mt1lQ</t>
+          <t>https://youtube.com/marciojerry</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/150418</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/81055</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
-        <v>160535</v>
+        <v>150418</v>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Marcon</t>
+          <t>Márcio Marinho</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>DIONILSO MATEUS MARCON</t>
+          <t>MÁRCIO CARLOS MARINHO</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>dep.marcon@camara.leg.br</t>
+          <t>dep.marciomarinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>@deputadomarcon</t>
+          <t>@deputadomarciomarinho</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadomarcon</t>
-        </is>
-      </c>
-      <c r="I333" s="2" t="inlineStr"/>
+          <t>https://instagram.com/deputadomarciomarinho</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCx3t_YQx8H-93UD5k9Mt1lQ</t>
+        </is>
+      </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/150418</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
-        <v>204431</v>
+        <v>160535</v>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Marcos Aurélio Sampaio</t>
+          <t>Marcon</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>MARCOS AURÉLIO  PÁDUA RIBEIRO GONÇALVES DE SAMPAIO</t>
+          <t>DIONILSO MATEUS MARCON</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>dep.marcosaureliosampaio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G334" s="2" t="inlineStr"/>
-      <c r="H334" s="2" t="inlineStr"/>
+          <t>dep.marcon@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>@deputadomarcon</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadomarcon</t>
+        </is>
+      </c>
       <c r="I334" s="2" t="inlineStr"/>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204431</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160535</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
-        <v>236375</v>
+        <v>204431</v>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Marcos Braz</t>
+          <t>Marcos Aurélio Sampaio</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>MARCOS TEIXEIRA BRAZ</t>
+          <t>MARCOS AURÉLIO  PÁDUA RIBEIRO GONÇALVES DE SAMPAIO</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>dep.marcosbraz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G335" s="2" t="inlineStr">
-        <is>
-          <t>@marcosbrazoficial</t>
-        </is>
-      </c>
-      <c r="H335" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/marcosbrazoficial</t>
-        </is>
-      </c>
+          <t>dep.marcosaureliosampaio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr"/>
+      <c r="H335" s="2" t="inlineStr"/>
       <c r="I335" s="2" t="inlineStr"/>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236375</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204431</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -18100,21 +18100,21 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>154700</v>
+        <v>141488</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Paulo Soares</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -18124,267 +18124,267 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.paulosoares@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr"/>
-      <c r="H402" s="2" t="inlineStr"/>
+          <t>dep.pauloteixeira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>@pauloteixeira13</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pauloteixeira13</t>
+        </is>
+      </c>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>141488</v>
+        <v>220630</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>@pauloteixeira13</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pauloteixeira13</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>220630</v>
+        <v>220667</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pedrocampos@camara.leg.br</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pedrocampospe</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pedrocampospe</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>220667</v>
+        <v>122974</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G405" s="2" t="inlineStr">
-        <is>
-          <t>@pedrocampospe</t>
-        </is>
-      </c>
-      <c r="H405" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrocampospe</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr"/>
+      <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>122974</v>
+        <v>204395</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G406" s="2" t="inlineStr"/>
-      <c r="H406" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I406" s="2" t="inlineStr"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>204395</v>
+        <v>122158</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H407" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedropaulo@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr"/>
+      <c r="H407" s="2" t="inlineStr"/>
       <c r="I407" s="2" t="inlineStr"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>122158</v>
+        <v>160604</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr"/>
@@ -18392,37 +18392,37 @@
       <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>160604</v>
+        <v>204406</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr"/>
@@ -18430,206 +18430,206 @@
       <c r="I409" s="2" t="inlineStr"/>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>204406</v>
+        <v>161440</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G410" s="2" t="inlineStr"/>
-      <c r="H410" s="2" t="inlineStr"/>
+          <t>dep.pezenti@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>@deputadopezenti</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
       <c r="I410" s="2" t="inlineStr"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>161440</v>
+        <v>204524</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>@deputadopezenti</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pinheirinhomg</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+        </is>
+      </c>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>204524</v>
+        <v>73486</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pompeodemattos@camara.leg.br</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@pompeodemattospdt</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
+          <t>https://instagram.com/pompeodemattospdt</t>
         </is>
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+          <t>https://youtube.com/PompeodeMattos</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>73486</v>
+        <v>160601</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>@pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PompeodeMattos</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr"/>
+      <c r="H413" s="2" t="inlineStr"/>
+      <c r="I413" s="2" t="inlineStr"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>160601</v>
+        <v>226075</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Priscila Costa</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>PRISCILA BEZERRA DA COSTA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -18639,449 +18639,449 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr"/>
-      <c r="H414" s="2" t="inlineStr"/>
+          <t>dep.priscilacosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>@priscilacosta</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/priscilacosta</t>
+        </is>
+      </c>
       <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>226075</v>
+        <v>220533</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Priscila Costa</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>PRISCILA BEZERRA DA COSTA</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.priscilacosta@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>@priscilacosta</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/priscilacosta</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr"/>
+          <t>https://instagram.com/reginaldo.veras</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/Reginaldoveras12</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>220533</v>
+        <v>204390</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.professoralcides@camara.leg.br</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@professoralcidesoficial</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
+          <t>https://instagram.com/professoralcidesoficial</t>
         </is>
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>204390</v>
+        <v>221338</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>@professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
+      <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>221338</v>
+        <v>160641</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr"/>
+          <t>dep.professoramarcivania@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>@profmarcivania</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
       <c r="I418" s="2" t="inlineStr"/>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>160641</v>
+        <v>220586</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
+          <t>dep.rafaelbrito@camara.leg.br</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>@profmarcivania</t>
+          <t>@rafaelbrito15</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>220586</v>
+        <v>233594</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="H420" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr"/>
+      <c r="H420" s="2" t="inlineStr"/>
+      <c r="I420" s="2" t="inlineStr"/>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>233594</v>
+        <v>220532</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr"/>
-      <c r="H421" s="2" t="inlineStr"/>
-      <c r="I421" s="2" t="inlineStr"/>
+          <t>dep.rafaelprudente@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>220532</v>
+        <v>220626</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>@rafaelprudentedep</t>
+          <t>@rafaelsimoesmg</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I422" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>220626</v>
+        <v>204567</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="H423" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr"/>
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>204567</v>
+        <v>74084</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -19091,85 +19091,89 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr"/>
-      <c r="H424" s="2" t="inlineStr"/>
-      <c r="I424" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>74084</v>
+        <v>74161</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H425" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
+          <t>dep.reginaldolopes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr"/>
+      <c r="H425" s="2" t="inlineStr"/>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>74161</v>
+        <v>220606</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -19179,54 +19183,50 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.reimont@camara.leg.br</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
-      <c r="I426" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I426" s="2" t="inlineStr"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>220606</v>
+        <v>178989</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Renata Abreu</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>RENATA HELLMEISTER DE ABREU MELO</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.renataabreu@camara.leg.br</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr"/>
@@ -19234,7 +19234,7 @@
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -9939,8 +9939,16 @@
           <t>dep.gilmarmachado@camara.leg.br</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>@gilmarmachadodep</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gilmarmachadodep</t>
+        </is>
+      </c>
       <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="2" t="inlineStr">
         <is>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -12054,161 +12054,161 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>74140</v>
+        <v>204472</v>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>José Carlos Araujo</t>
+          <t>José Medeiros</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ CARLOS LEÃO DE ARAÚJO</t>
+          <t>JOSE ANTONIO DOS SANTOS MEDEIROS</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>dep.josecarlosaraujo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr"/>
+          <t>dep.josemedeiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>@josemedeirosmt</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/josemedeirosmt</t>
+        </is>
+      </c>
       <c r="I265" s="2" t="inlineStr"/>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74140</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204472</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>204472</v>
+        <v>204391</v>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>José Medeiros</t>
+          <t>José Nelto</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO DOS SANTOS MEDEIROS</t>
+          <t>JOSÉ NELTO LAGARES DAS MERCEZ</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>dep.josemedeiros@camara.leg.br</t>
+          <t>dep.josenelto@camara.leg.br</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>@josemedeirosmt</t>
+          <t>@joseneltooficial</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/josemedeirosmt</t>
+          <t>https://instagram.com/joseneltooficial</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204472</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204391</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>204391</v>
+        <v>74079</v>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>José Nelto</t>
+          <t>José Priante</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ NELTO LAGARES DAS MERCEZ</t>
+          <t>JOSÉ BENITO PRIANTE JÚNIOR</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>dep.josenelto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>@joseneltooficial</t>
-        </is>
-      </c>
-      <c r="H267" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/joseneltooficial</t>
-        </is>
-      </c>
+          <t>dep.josepriante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
       <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204391</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74079</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>74079</v>
+        <v>74554</v>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>José Priante</t>
+          <t>José Rocha</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ BENITO PRIANTE JÚNIOR</t>
+          <t>JOSÉ ALVES ROCHA</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>dep.josepriante@camara.leg.br</t>
+          <t>dep.joserocha@camara.leg.br</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr"/>
@@ -12216,27 +12216,27 @@
       <c r="I268" s="2" t="inlineStr"/>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74079</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74554</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>74554</v>
+        <v>209189</v>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>José Rocha</t>
+          <t>Joseildo Ramos</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ ALVES ROCHA</t>
+          <t>JOSEILDO RIBEIRO RAMOS</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -12246,127 +12246,127 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>dep.joserocha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr"/>
+          <t>dep.joseildoramos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>@joseildoramos</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/joseildoramos</t>
+        </is>
+      </c>
       <c r="I269" s="2" t="inlineStr"/>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74554</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209189</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>209189</v>
+        <v>220578</v>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Joseildo Ramos</t>
+          <t>Josenildo</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>JOSEILDO RIBEIRO RAMOS</t>
+          <t>JOSENILDO SANTOS ABRANTES</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>dep.joseildoramos@camara.leg.br</t>
+          <t>dep.josenildo@camara.leg.br</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>@joseildoramos</t>
+          <t>@josenildoap_</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/joseildoramos</t>
+          <t>https://instagram.com/josenildoap_</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209189</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220578</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>220578</v>
+        <v>204563</v>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Josenildo</t>
+          <t>Josimar Maranhãozinho</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>JOSENILDO SANTOS ABRANTES</t>
+          <t>JOSIMAR CUNHA RODRIGUES</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>dep.josenildo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G271" s="2" t="inlineStr">
-        <is>
-          <t>@josenildoap_</t>
-        </is>
-      </c>
-      <c r="H271" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/josenildoap_</t>
-        </is>
-      </c>
+          <t>dep.josimarmaranhaozinho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
       <c r="I271" s="2" t="inlineStr"/>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220578</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204563</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>204563</v>
+        <v>215043</v>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Josimar Maranhãozinho</t>
+          <t>Josivaldo JP</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>JOSIMAR CUNHA RODRIGUES</t>
+          <t>JOSIVALDO DOS SANTOS MELO</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -12376,231 +12376,243 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>dep.josimarmaranhaozinho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr"/>
+          <t>dep.josivaldojp@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>@jpdeputado</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jpdeputado</t>
+        </is>
+      </c>
       <c r="I272" s="2" t="inlineStr"/>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204563</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/215043</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>215043</v>
+        <v>204474</v>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Josivaldo JP</t>
+          <t>Juarez Costa</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>JOSIVALDO DOS SANTOS MELO</t>
+          <t>JUAREZ ALVES DA COSTA</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>dep.josivaldojp@camara.leg.br</t>
+          <t>dep.juarezcosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>@jpdeputado</t>
+          <t>@juarezcostamt</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/jpdeputado</t>
-        </is>
-      </c>
-      <c r="I273" s="2" t="inlineStr"/>
+          <t>https://instagram.com/juarezcostamt</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCKKA7s-2Lo6xKtZlgahT-aA</t>
+        </is>
+      </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/215043</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204474</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>204474</v>
+        <v>220559</v>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Juarez Costa</t>
+          <t>Julia Zanatta</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>JUAREZ ALVES DA COSTA</t>
+          <t>JULIA PEDROSO ZANATTA</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>dep.juarezcosta@camara.leg.br</t>
+          <t>dep.juliazanatta@camara.leg.br</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>@juarezcostamt</t>
+          <t>@juliazanattasc</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juarezcostamt</t>
+          <t>https://instagram.com/juliazanattasc</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCKKA7s-2Lo6xKtZlgahT-aA</t>
+          <t>https://youtube.com/channel/UC-xMxlTPP-xGmOry0wx2sxw</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204474</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220559</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>220559</v>
+        <v>220640</v>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Julia Zanatta</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>JULIA PEDROSO ZANATTA</t>
+          <t>JULIANA CARDOSO</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>dep.juliazanatta@camara.leg.br</t>
+          <t>dep.julianacardoso@camara.leg.br</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>@juliazanattasc</t>
+          <t>@julianacardoso_pt</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juliazanattasc</t>
+          <t>https://instagram.com/julianacardoso_pt</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC-xMxlTPP-xGmOry0wx2sxw</t>
+          <t>https://youtube.com/julianacardosopt</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220559</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220640</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>220640</v>
+        <v>66385</v>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Juliana Cardoso</t>
+          <t>Julio Arcoverde</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>JULIANA CARDOSO</t>
+          <t>JULIO FERRAZ ARCOVERDE</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>dep.julianacardoso@camara.leg.br</t>
+          <t>dep.julioarcoverde@camara.leg.br</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>@julianacardoso_pt</t>
+          <t>@julioarcoverde</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/julianacardoso_pt</t>
+          <t>https://instagram.com/julioarcoverde</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/julianacardosopt</t>
+          <t>https://youtube.com/julioarcoverde</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220640</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/66385</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>66385</v>
+        <v>74317</v>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Julio Arcoverde</t>
+          <t>Júlio Cesar</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>JULIO FERRAZ ARCOVERDE</t>
+          <t>JÚLIO CÉSAR DE CARVALHO LIMA</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -12610,147 +12622,147 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>dep.julioarcoverde@camara.leg.br</t>
+          <t>dep.juliocesar@camara.leg.br</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>@julioarcoverde</t>
+          <t>@deputadojuliocesar</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/julioarcoverde</t>
+          <t>https://instagram.com/deputadojuliocesar</t>
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/julioarcoverde</t>
+          <t>https://youtube.com/deputadojuliocesarpi</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/66385</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74317</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>74317</v>
+        <v>204372</v>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Júlio Cesar</t>
+          <t>Julio Cesar Ribeiro</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>JÚLIO CÉSAR DE CARVALHO LIMA</t>
+          <t>JULIO CESAR RIBEIRO</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>dep.juliocesar@camara.leg.br</t>
+          <t>dep.juliocesarribeiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>@deputadojuliocesar</t>
+          <t>@juliocesarribeiro</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadojuliocesar</t>
+          <t>https://instagram.com/juliocesarribeiro</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/deputadojuliocesarpi</t>
+          <t>https://youtube.com/JulioCesarRibeiro</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74317</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204372</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>204372</v>
+        <v>74253</v>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Julio Cesar Ribeiro</t>
+          <t>Julio Lopes</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>JULIO CESAR RIBEIRO</t>
+          <t>JULIO LUIZ BAPTISTA LOPES</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>dep.juliocesarribeiro@camara.leg.br</t>
+          <t>dep.juliolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>@juliocesarribeiro</t>
+          <t>@juliolopes_rio</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juliocesarribeiro</t>
+          <t>https://instagram.com/juliolopes_rio</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/JulioCesarRibeiro</t>
+          <t>https://youtube.com/JulioLopesRio</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204372</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74253</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>74253</v>
+        <v>204457</v>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Julio Lopes</t>
+          <t>Juninho do Pneu</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>JULIO LUIZ BAPTISTA LOPES</t>
+          <t>ROGERIO TEIXEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -12760,361 +12772,361 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>dep.juliolopes@camara.leg.br</t>
+          <t>dep.juninhodopneu@camara.leg.br</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>@juliolopes_rio</t>
+          <t>@juninhodopneu</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juliolopes_rio</t>
-        </is>
-      </c>
-      <c r="I280" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/JulioLopesRio</t>
-        </is>
-      </c>
+          <t>https://instagram.com/juninhodopneu</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr"/>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74253</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204457</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>204457</v>
+        <v>204520</v>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Juninho do Pneu</t>
+          <t>Junio Amaral</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>ROGERIO TEIXEIRA JUNIOR</t>
+          <t>GERALDO JUNIO DO AMARAL</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>dep.juninhodopneu@camara.leg.br</t>
+          <t>dep.junioamaral@camara.leg.br</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>@juninhodopneu</t>
+          <t>@junioamaraldm</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juninhodopneu</t>
+          <t>https://instagram.com/junioamaraldm</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204457</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204520</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>204520</v>
+        <v>204497</v>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Junio Amaral</t>
+          <t>Júnior Ferrari</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>GERALDO JUNIO DO AMARAL</t>
+          <t>JOÃO FERRARI JÚNIOR</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>dep.junioamaral@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>@junioamaraldm</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/junioamaraldm</t>
-        </is>
-      </c>
+          <t>dep.juniorferrari@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
       <c r="I282" s="2" t="inlineStr"/>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204520</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204497</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>204497</v>
+        <v>204574</v>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Júnior Ferrari</t>
+          <t>Junior Lourenço</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>JOÃO FERRARI JÚNIOR</t>
+          <t>JOSE LOURENÇO BOMFIM JUNIOR</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>dep.juniorferrari@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr"/>
+          <t>dep.juniorlourenco@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>@juniorlourenco2200</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/juniorlourenco2200</t>
+        </is>
+      </c>
       <c r="I283" s="2" t="inlineStr"/>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204497</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204574</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>204574</v>
+        <v>204550</v>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Junior Lourenço</t>
+          <t>Júnior Mano</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>JOSE LOURENÇO BOMFIM JUNIOR</t>
+          <t>ANTÔNIO LUIZ RODRIGUES MANO JÚNIOR</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>dep.juniorlourenco@camara.leg.br</t>
+          <t>dep.juniormano@camara.leg.br</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>@juniorlourenco2200</t>
+          <t>@juniormanodep</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/juniorlourenco2200</t>
-        </is>
-      </c>
-      <c r="I284" s="2" t="inlineStr"/>
+          <t>https://instagram.com/juniormanodep</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadojuniormano</t>
+        </is>
+      </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204550</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>204550</v>
+        <v>178886</v>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Júnior Mano</t>
+          <t>Juscelino Filho</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO LUIZ RODRIGUES MANO JÚNIOR</t>
+          <t>JOSE JUSCELINO DOS SANTOS REZENDE FILHO</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>dep.juniormano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>@juniormanodep</t>
-        </is>
-      </c>
-      <c r="H285" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/juniormanodep</t>
-        </is>
-      </c>
-      <c r="I285" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadojuniormano</t>
-        </is>
-      </c>
+          <t>dep.juscelinofilho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+      <c r="I285" s="2" t="inlineStr"/>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204550</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178886</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>178886</v>
+        <v>220677</v>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Juscelino Filho</t>
+          <t>Keniston Braga</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>JOSE JUSCELINO DOS SANTOS REZENDE FILHO</t>
+          <t>KENISTON DE JESUS REGO BRAGA</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>dep.juscelinofilho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr"/>
-      <c r="I286" s="2" t="inlineStr"/>
+          <t>dep.kenistonbraga@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>@kenistonoficial</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kenistonoficial</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/KenistonOficial</t>
+        </is>
+      </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178886</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220677</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>220677</v>
+        <v>162067</v>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Keniston Braga</t>
+          <t>Kiko Celeguim</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>KENISTON DE JESUS REGO BRAGA</t>
+          <t>FRANCISCO DANIEL CELEGUIM DE MORAIS</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>dep.kenistonbraga@camara.leg.br</t>
+          <t>dep.kikoceleguim@camara.leg.br</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>@kenistonoficial</t>
+          <t>@kiko.celeguim</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/kenistonoficial</t>
+          <t>https://instagram.com/kiko.celeguim</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/c/KenistonOficial</t>
+          <t>https://youtube.com/KikoCeleguimoficial</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220677</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162067</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>162067</v>
+        <v>204536</v>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Kiko Celeguim</t>
+          <t>Kim Kataguiri</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO DANIEL CELEGUIM DE MORAIS</t>
+          <t>KIM PATROCA KATAGUIRI</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>MISSÃO</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -13124,142 +13136,130 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>dep.kikoceleguim@camara.leg.br</t>
+          <t>dep.kimkataguiri@camara.leg.br</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>@kiko.celeguim</t>
+          <t>@kimkataguiri</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/kiko.celeguim</t>
+          <t>https://instagram.com/kimkataguiri</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/KikoCeleguimoficial</t>
+          <t>https://youtube.com/kimkataguiri</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162067</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204536</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>204536</v>
+        <v>98057</v>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Kim Kataguiri</t>
+          <t>Lafayette de Andrada</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>KIM PATROCA KATAGUIRI</t>
+          <t>LAFAYETTE LUIZ DOORGAL DE ANDRADA</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>MISSÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>dep.kimkataguiri@camara.leg.br</t>
+          <t>dep.lafayettedeandrada@camara.leg.br</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>@kimkataguiri</t>
+          <t>@lafayetteandrada</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/kimkataguiri</t>
+          <t>https://instagram.com/lafayetteandrada</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/kimkataguiri</t>
+          <t>https://youtube.com/channel/UC5f8X2JAnafqV7bPLmDeZGw</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204536</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/98057</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>98057</v>
+        <v>74856</v>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Lafayette de Andrada</t>
+          <t>Laura Carneiro</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>LAFAYETTE LUIZ DOORGAL DE ANDRADA</t>
+          <t>MARIA LAURA MONTEZA DE SOUZA CARNEIRO</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>dep.lafayettedeandrada@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G290" s="2" t="inlineStr">
-        <is>
-          <t>@lafayetteandrada</t>
-        </is>
-      </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/lafayetteandrada</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC5f8X2JAnafqV7bPLmDeZGw</t>
-        </is>
-      </c>
+          <t>dep.lauracarneiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr"/>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/98057</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74856</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>74856</v>
+        <v>178832</v>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Laura Carneiro</t>
+          <t>Leandre</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>MARIA LAURA MONTEZA DE SOUZA CARNEIRO</t>
+          <t>LEANDRE DAL PONTE</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>dep.lauracarneiro@camara.leg.br</t>
+          <t>dep.leandre@camara.leg.br</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr"/>
@@ -13282,37 +13282,37 @@
       <c r="I291" s="2" t="inlineStr"/>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74856</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178832</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>178832</v>
+        <v>220566</v>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Leandre</t>
+          <t>Lêda Borges</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>LEANDRE DAL PONTE</t>
+          <t>Lêda Borges de Moura</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>dep.leandre@camara.leg.br</t>
+          <t>dep.ledaborges@camara.leg.br</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr"/>
@@ -13320,22 +13320,22 @@
       <c r="I292" s="2" t="inlineStr"/>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178832</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220566</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>220566</v>
+        <v>80815</v>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Lêda Borges</t>
+          <t>Leo Prates</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Lêda Borges de Moura</t>
+          <t>LEONARDO SILVA PRATES</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -13345,20 +13345,28 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>dep.ledaborges@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr"/>
+          <t>dep.leoprates@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>@leoprates</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/leoprates</t>
+        </is>
+      </c>
       <c r="I293" s="2" t="inlineStr"/>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220566</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/80815</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -21905,8 +21905,16 @@
           <t>dep.tiaomedeiros@camara.leg.br</t>
         </is>
       </c>
-      <c r="G487" s="2" t="inlineStr"/>
-      <c r="H487" s="2" t="inlineStr"/>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>@tiaomedeirospr</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tiaomedeirospr</t>
+        </is>
+      </c>
       <c r="I487" s="2" t="inlineStr"/>
       <c r="J487" s="2" t="inlineStr">
         <is>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -10487,8 +10487,16 @@
           <t>dep.gustinhoribeiro@camara.leg.br</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>@gustinho</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gustinho</t>
+        </is>
+      </c>
       <c r="I228" s="2" t="inlineStr"/>
       <c r="J228" s="2" t="inlineStr">
         <is>
